--- a/artfynd/A 52547-2020 artfynd.xlsx
+++ b/artfynd/A 52547-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52547-2020 artfynd.xlsx
+++ b/artfynd/A 52547-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3588,2467 +3588,6 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>112605517</v>
-      </c>
-      <c r="B27" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Lillsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>692748</v>
-      </c>
-      <c r="R27" t="n">
-        <v>7149407</v>
-      </c>
-      <c r="S27" t="n">
-        <v>10</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>112605516</v>
-      </c>
-      <c r="B28" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Lillsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>692723</v>
-      </c>
-      <c r="R28" t="n">
-        <v>7149432</v>
-      </c>
-      <c r="S28" t="n">
-        <v>10</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>112605534</v>
-      </c>
-      <c r="B29" t="n">
-        <v>77608</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Lillsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>693059</v>
-      </c>
-      <c r="R29" t="n">
-        <v>7149303</v>
-      </c>
-      <c r="S29" t="n">
-        <v>10</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>112605524</v>
-      </c>
-      <c r="B30" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Lillsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>692952</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7149192</v>
-      </c>
-      <c r="S30" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>112605541</v>
-      </c>
-      <c r="B31" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Lillsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>692921</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7149453</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>112605523</v>
-      </c>
-      <c r="B32" t="n">
-        <v>89735</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Lillsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>692944</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7149211</v>
-      </c>
-      <c r="S32" t="n">
-        <v>10</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>112605542</v>
-      </c>
-      <c r="B33" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Lillsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>692887</v>
-      </c>
-      <c r="R33" t="n">
-        <v>7149444</v>
-      </c>
-      <c r="S33" t="n">
-        <v>10</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>112605543</v>
-      </c>
-      <c r="B34" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Lillsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>692897</v>
-      </c>
-      <c r="R34" t="n">
-        <v>7149418</v>
-      </c>
-      <c r="S34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>112605519</v>
-      </c>
-      <c r="B35" t="n">
-        <v>91055</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>5966</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Lillsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>692917</v>
-      </c>
-      <c r="R35" t="n">
-        <v>7149236</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>112605520</v>
-      </c>
-      <c r="B36" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Lillsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>692942</v>
-      </c>
-      <c r="R36" t="n">
-        <v>7149237</v>
-      </c>
-      <c r="S36" t="n">
-        <v>10</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>112605526</v>
-      </c>
-      <c r="B37" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Lillsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>692987</v>
-      </c>
-      <c r="R37" t="n">
-        <v>7149165</v>
-      </c>
-      <c r="S37" t="n">
-        <v>10</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>112605522</v>
-      </c>
-      <c r="B38" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Lillsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>692931</v>
-      </c>
-      <c r="R38" t="n">
-        <v>7149216</v>
-      </c>
-      <c r="S38" t="n">
-        <v>10</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>112605536</v>
-      </c>
-      <c r="B39" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Lillsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>693047</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7149306</v>
-      </c>
-      <c r="S39" t="n">
-        <v>10</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>112605535</v>
-      </c>
-      <c r="B40" t="n">
-        <v>78448</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Lillsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>693054</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7149307</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>112605529</v>
-      </c>
-      <c r="B41" t="n">
-        <v>90012</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>65</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Fläckporing</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Anthoporia albobrunnea</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Lillsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>693025</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7149119</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>112605532</v>
-      </c>
-      <c r="B42" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Lillsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>693045</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7149281</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>112605530</v>
-      </c>
-      <c r="B43" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Lillsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>693089</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7149220</v>
-      </c>
-      <c r="S43" t="n">
-        <v>10</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>112605521</v>
-      </c>
-      <c r="B44" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Lillsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>692936</v>
-      </c>
-      <c r="R44" t="n">
-        <v>7149224</v>
-      </c>
-      <c r="S44" t="n">
-        <v>10</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>112605525</v>
-      </c>
-      <c r="B45" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Lillsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>692970</v>
-      </c>
-      <c r="R45" t="n">
-        <v>7149178</v>
-      </c>
-      <c r="S45" t="n">
-        <v>10</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>112605527</v>
-      </c>
-      <c r="B46" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Lillsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>692996</v>
-      </c>
-      <c r="R46" t="n">
-        <v>7149157</v>
-      </c>
-      <c r="S46" t="n">
-        <v>10</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>112605518</v>
-      </c>
-      <c r="B47" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Lillsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>692898</v>
-      </c>
-      <c r="R47" t="n">
-        <v>7149277</v>
-      </c>
-      <c r="S47" t="n">
-        <v>10</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>112605531</v>
-      </c>
-      <c r="B48" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Lillsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>693086</v>
-      </c>
-      <c r="R48" t="n">
-        <v>7149232</v>
-      </c>
-      <c r="S48" t="n">
-        <v>10</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>112605533</v>
-      </c>
-      <c r="B49" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Lillsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>693055</v>
-      </c>
-      <c r="R49" t="n">
-        <v>7149291</v>
-      </c>
-      <c r="S49" t="n">
-        <v>10</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52547-2020 artfynd.xlsx
+++ b/artfynd/A 52547-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3588,6 +3588,4882 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127412328</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92652</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>692931</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7149192</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127412332</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>692625</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7149521</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127412329</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>692950</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7149192</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127412327</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>692929</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7149201</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127412322</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>692932</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7149288</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127412326</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>692934</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7149219</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127412365</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>693089</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7149223</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127412334</v>
+      </c>
+      <c r="B34" t="n">
+        <v>5492</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>692673</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7149439</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127412363</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>693054</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7149264</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127412324</v>
+      </c>
+      <c r="B36" t="n">
+        <v>92604</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>149</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tallgråticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Boletopsis grisea</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Peck) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>692937</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7149228</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127412360</v>
+      </c>
+      <c r="B37" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>692978</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7149291</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127412367</v>
+      </c>
+      <c r="B38" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>693081</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7149184</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127412330</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92652</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>692974</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7149201</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127412321</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92610</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>692916</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7149304</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127412351</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79603</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>692985</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7149378</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127412343</v>
+      </c>
+      <c r="B42" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>692872</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7149487</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127412358</v>
+      </c>
+      <c r="B43" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>692977</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7149327</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127412368</v>
+      </c>
+      <c r="B44" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>693101</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7149176</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127412346</v>
+      </c>
+      <c r="B45" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>692896</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7149409</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127412348</v>
+      </c>
+      <c r="B46" t="n">
+        <v>5492</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>692895</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7149371</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127412339</v>
+      </c>
+      <c r="B47" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>692742</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7149553</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127412342</v>
+      </c>
+      <c r="B48" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>692822</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7149491</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127412349</v>
+      </c>
+      <c r="B49" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>692946</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7149378</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127412352</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79632</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>692989</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7149374</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>127412320</v>
+      </c>
+      <c r="B51" t="n">
+        <v>92642</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>692916</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7149304</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>127412341</v>
+      </c>
+      <c r="B52" t="n">
+        <v>92610</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>692724</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7149487</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>127412359</v>
+      </c>
+      <c r="B53" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>692987</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7149303</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>127412338</v>
+      </c>
+      <c r="B54" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>692701</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7149567</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>127412366</v>
+      </c>
+      <c r="B55" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>693119</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7149224</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>127412323</v>
+      </c>
+      <c r="B56" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>692957</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7149247</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>127412361</v>
+      </c>
+      <c r="B57" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>693017</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7149215</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>127412325</v>
+      </c>
+      <c r="B58" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>692939</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7149230</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127412347</v>
+      </c>
+      <c r="B59" t="n">
+        <v>78773</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>692899</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7149399</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>127412345</v>
+      </c>
+      <c r="B60" t="n">
+        <v>92644</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>692899</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7149426</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>127412362</v>
+      </c>
+      <c r="B61" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>693013</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7149208</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>127412333</v>
+      </c>
+      <c r="B62" t="n">
+        <v>92608</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>692649</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7149598</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>127412331</v>
+      </c>
+      <c r="B63" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>692989</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7149194</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>127412344</v>
+      </c>
+      <c r="B64" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>692854</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7149427</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>127412364</v>
+      </c>
+      <c r="B65" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>693060</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7149216</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>127412370</v>
+      </c>
+      <c r="B66" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>693118</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7149155</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>127412356</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>692981</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7149358</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>127412350</v>
+      </c>
+      <c r="B68" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>692958</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7149383</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>127412355</v>
+      </c>
+      <c r="B69" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>692985</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7149369</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>127412353</v>
+      </c>
+      <c r="B70" t="n">
+        <v>78773</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>692989</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7149374</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>127412357</v>
+      </c>
+      <c r="B71" t="n">
+        <v>92644</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>692963</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7149329</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>127412340</v>
+      </c>
+      <c r="B72" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>692693</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7149468</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52547-2020 artfynd.xlsx
+++ b/artfynd/A 52547-2020 artfynd.xlsx
@@ -3908,10 +3908,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127412327</v>
+        <v>127412322</v>
       </c>
       <c r="B30" t="n">
-        <v>92628</v>
+        <v>92616</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3919,21 +3919,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>692929</v>
+        <v>692932</v>
       </c>
       <c r="R30" t="n">
-        <v>7149201</v>
+        <v>7149288</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4014,32 +4014,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127412322</v>
+        <v>127412326</v>
       </c>
       <c r="B31" t="n">
-        <v>92616</v>
+        <v>92632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>692932</v>
+        <v>692934</v>
       </c>
       <c r="R31" t="n">
-        <v>7149288</v>
+        <v>7149219</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4120,32 +4120,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127412326</v>
+        <v>127412327</v>
       </c>
       <c r="B32" t="n">
-        <v>92632</v>
+        <v>92628</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>692934</v>
+        <v>692929</v>
       </c>
       <c r="R32" t="n">
-        <v>7149219</v>
+        <v>7149201</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4226,7 +4226,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127412365</v>
+        <v>127412363</v>
       </c>
       <c r="B33" t="n">
         <v>92616</v>
@@ -4265,10 +4265,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>693089</v>
+        <v>693054</v>
       </c>
       <c r="R33" t="n">
-        <v>7149223</v>
+        <v>7149264</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4332,32 +4332,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127412334</v>
+        <v>127412365</v>
       </c>
       <c r="B34" t="n">
-        <v>5492</v>
+        <v>92616</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>692673</v>
+        <v>693089</v>
       </c>
       <c r="R34" t="n">
-        <v>7149439</v>
+        <v>7149223</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4438,32 +4438,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127412363</v>
+        <v>127412334</v>
       </c>
       <c r="B35" t="n">
-        <v>92616</v>
+        <v>5492</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>693054</v>
+        <v>692673</v>
       </c>
       <c r="R35" t="n">
-        <v>7149264</v>
+        <v>7149439</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4544,32 +4544,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127412324</v>
+        <v>127412360</v>
       </c>
       <c r="B36" t="n">
-        <v>92604</v>
+        <v>92632</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>149</v>
+        <v>2059</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>692937</v>
+        <v>692978</v>
       </c>
       <c r="R36" t="n">
-        <v>7149228</v>
+        <v>7149291</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127412360</v>
+        <v>127412324</v>
       </c>
       <c r="B37" t="n">
-        <v>92632</v>
+        <v>92604</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2059</v>
+        <v>149</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>692978</v>
+        <v>692937</v>
       </c>
       <c r="R37" t="n">
-        <v>7149291</v>
+        <v>7149228</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4862,10 +4862,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127412330</v>
+        <v>127412321</v>
       </c>
       <c r="B39" t="n">
-        <v>92652</v>
+        <v>92610</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4873,21 +4873,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>692974</v>
+        <v>692916</v>
       </c>
       <c r="R39" t="n">
-        <v>7149201</v>
+        <v>7149304</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4968,10 +4968,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127412321</v>
+        <v>127412330</v>
       </c>
       <c r="B40" t="n">
-        <v>92610</v>
+        <v>92652</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4979,21 +4979,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>692916</v>
+        <v>692974</v>
       </c>
       <c r="R40" t="n">
-        <v>7149304</v>
+        <v>7149201</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5286,7 +5286,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127412358</v>
+        <v>127412346</v>
       </c>
       <c r="B43" t="n">
         <v>92616</v>
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>692977</v>
+        <v>692896</v>
       </c>
       <c r="R43" t="n">
-        <v>7149327</v>
+        <v>7149409</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5498,7 +5498,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127412346</v>
+        <v>127412358</v>
       </c>
       <c r="B45" t="n">
         <v>92616</v>
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>692896</v>
+        <v>692977</v>
       </c>
       <c r="R45" t="n">
-        <v>7149409</v>
+        <v>7149327</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5710,7 +5710,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127412339</v>
+        <v>127412342</v>
       </c>
       <c r="B47" t="n">
         <v>92616</v>
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>692742</v>
+        <v>692822</v>
       </c>
       <c r="R47" t="n">
-        <v>7149553</v>
+        <v>7149491</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5816,7 +5816,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127412342</v>
+        <v>127412339</v>
       </c>
       <c r="B48" t="n">
         <v>92616</v>
@@ -5855,10 +5855,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>692822</v>
+        <v>692742</v>
       </c>
       <c r="R48" t="n">
-        <v>7149491</v>
+        <v>7149553</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6028,10 +6028,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127412352</v>
+        <v>127412320</v>
       </c>
       <c r="B50" t="n">
-        <v>79632</v>
+        <v>92642</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>5448</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>692989</v>
+        <v>692916</v>
       </c>
       <c r="R50" t="n">
-        <v>7149374</v>
+        <v>7149304</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6134,10 +6134,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127412320</v>
+        <v>127412352</v>
       </c>
       <c r="B51" t="n">
-        <v>92642</v>
+        <v>79632</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5448</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>692916</v>
+        <v>692989</v>
       </c>
       <c r="R51" t="n">
-        <v>7149304</v>
+        <v>7149374</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6452,32 +6452,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127412338</v>
+        <v>127412366</v>
       </c>
       <c r="B54" t="n">
-        <v>92616</v>
+        <v>92632</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>692701</v>
+        <v>693119</v>
       </c>
       <c r="R54" t="n">
-        <v>7149567</v>
+        <v>7149224</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6558,32 +6558,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412366</v>
+        <v>127412338</v>
       </c>
       <c r="B55" t="n">
-        <v>92632</v>
+        <v>92616</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6597,10 +6597,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>693119</v>
+        <v>692701</v>
       </c>
       <c r="R55" t="n">
-        <v>7149224</v>
+        <v>7149567</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6770,7 +6770,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127412361</v>
+        <v>127412325</v>
       </c>
       <c r="B57" t="n">
         <v>92632</v>
@@ -6809,10 +6809,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>693017</v>
+        <v>692939</v>
       </c>
       <c r="R57" t="n">
-        <v>7149215</v>
+        <v>7149230</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6876,7 +6876,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127412325</v>
+        <v>127412361</v>
       </c>
       <c r="B58" t="n">
         <v>92632</v>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>692939</v>
+        <v>693017</v>
       </c>
       <c r="R58" t="n">
-        <v>7149230</v>
+        <v>7149215</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7088,32 +7088,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412345</v>
+        <v>127412331</v>
       </c>
       <c r="B60" t="n">
-        <v>92644</v>
+        <v>92616</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7127,10 +7127,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>692899</v>
+        <v>692989</v>
       </c>
       <c r="R60" t="n">
-        <v>7149426</v>
+        <v>7149194</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7194,7 +7194,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412362</v>
+        <v>127412370</v>
       </c>
       <c r="B61" t="n">
         <v>92616</v>
@@ -7233,10 +7233,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>693013</v>
+        <v>693118</v>
       </c>
       <c r="R61" t="n">
-        <v>7149208</v>
+        <v>7149155</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7300,10 +7300,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127412333</v>
+        <v>127412364</v>
       </c>
       <c r="B62" t="n">
-        <v>92608</v>
+        <v>92632</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7311,21 +7311,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>692649</v>
+        <v>693060</v>
       </c>
       <c r="R62" t="n">
-        <v>7149598</v>
+        <v>7149216</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7406,32 +7406,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127412331</v>
+        <v>127412333</v>
       </c>
       <c r="B63" t="n">
-        <v>92616</v>
+        <v>92608</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>692989</v>
+        <v>692649</v>
       </c>
       <c r="R63" t="n">
-        <v>7149194</v>
+        <v>7149598</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7618,32 +7618,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412364</v>
+        <v>127412362</v>
       </c>
       <c r="B65" t="n">
-        <v>92632</v>
+        <v>92616</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7657,10 +7657,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>693060</v>
+        <v>693013</v>
       </c>
       <c r="R65" t="n">
-        <v>7149216</v>
+        <v>7149208</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7724,32 +7724,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127412370</v>
+        <v>127412345</v>
       </c>
       <c r="B66" t="n">
-        <v>92616</v>
+        <v>92644</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>693118</v>
+        <v>692899</v>
       </c>
       <c r="R66" t="n">
-        <v>7149155</v>
+        <v>7149426</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7936,32 +7936,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127412350</v>
+        <v>127412353</v>
       </c>
       <c r="B68" t="n">
-        <v>92628</v>
+        <v>78773</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7975,10 +7975,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>692958</v>
+        <v>692989</v>
       </c>
       <c r="R68" t="n">
-        <v>7149383</v>
+        <v>7149374</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8042,32 +8042,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127412355</v>
+        <v>127412357</v>
       </c>
       <c r="B69" t="n">
-        <v>92616</v>
+        <v>92644</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -8081,10 +8081,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>692985</v>
+        <v>692963</v>
       </c>
       <c r="R69" t="n">
-        <v>7149369</v>
+        <v>7149329</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8148,32 +8148,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127412353</v>
+        <v>127412350</v>
       </c>
       <c r="B70" t="n">
-        <v>78773</v>
+        <v>92628</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>692989</v>
+        <v>692958</v>
       </c>
       <c r="R70" t="n">
-        <v>7149374</v>
+        <v>7149383</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8254,32 +8254,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127412357</v>
+        <v>127412355</v>
       </c>
       <c r="B71" t="n">
-        <v>92644</v>
+        <v>92616</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8293,10 +8293,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>692963</v>
+        <v>692985</v>
       </c>
       <c r="R71" t="n">
-        <v>7149329</v>
+        <v>7149369</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>

--- a/artfynd/A 52547-2020 artfynd.xlsx
+++ b/artfynd/A 52547-2020 artfynd.xlsx
@@ -3590,10 +3590,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127412328</v>
+        <v>127412326</v>
       </c>
       <c r="B27" t="n">
-        <v>92652</v>
+        <v>92636</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3601,21 +3601,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>692931</v>
+        <v>692934</v>
       </c>
       <c r="R27" t="n">
-        <v>7149192</v>
+        <v>7149219</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127412332</v>
+        <v>127412327</v>
       </c>
       <c r="B28" t="n">
-        <v>92628</v>
+        <v>92632</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>692625</v>
+        <v>692929</v>
       </c>
       <c r="R28" t="n">
-        <v>7149521</v>
+        <v>7149201</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3805,7 +3805,7 @@
         <v>127412329</v>
       </c>
       <c r="B29" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>127412322</v>
       </c>
       <c r="B30" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4014,32 +4014,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127412326</v>
+        <v>127412332</v>
       </c>
       <c r="B31" t="n">
         <v>92632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>692934</v>
+        <v>692625</v>
       </c>
       <c r="R31" t="n">
-        <v>7149219</v>
+        <v>7149521</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4120,32 +4120,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127412327</v>
+        <v>127412328</v>
       </c>
       <c r="B32" t="n">
-        <v>92628</v>
+        <v>92656</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>692929</v>
+        <v>692931</v>
       </c>
       <c r="R32" t="n">
-        <v>7149201</v>
+        <v>7149192</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4229,7 +4229,7 @@
         <v>127412363</v>
       </c>
       <c r="B33" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>127412365</v>
       </c>
       <c r="B34" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>127412334</v>
       </c>
       <c r="B35" t="n">
-        <v>5492</v>
+        <v>5493</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4544,32 +4544,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127412360</v>
+        <v>127412324</v>
       </c>
       <c r="B36" t="n">
-        <v>92632</v>
+        <v>92608</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2059</v>
+        <v>149</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>692978</v>
+        <v>692937</v>
       </c>
       <c r="R36" t="n">
-        <v>7149291</v>
+        <v>7149228</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127412324</v>
+        <v>127412360</v>
       </c>
       <c r="B37" t="n">
-        <v>92604</v>
+        <v>92636</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>149</v>
+        <v>2059</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>692937</v>
+        <v>692978</v>
       </c>
       <c r="R37" t="n">
-        <v>7149228</v>
+        <v>7149291</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4759,7 +4759,7 @@
         <v>127412367</v>
       </c>
       <c r="B38" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>127412321</v>
       </c>
       <c r="B39" t="n">
-        <v>92610</v>
+        <v>92614</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>127412330</v>
       </c>
       <c r="B40" t="n">
-        <v>92652</v>
+        <v>92656</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>127412351</v>
       </c>
       <c r="B41" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>127412343</v>
       </c>
       <c r="B42" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>127412346</v>
       </c>
       <c r="B43" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>127412368</v>
       </c>
       <c r="B44" t="n">
-        <v>92628</v>
+        <v>92632</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>127412358</v>
       </c>
       <c r="B45" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>127412348</v>
       </c>
       <c r="B46" t="n">
-        <v>5492</v>
+        <v>5493</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5710,10 +5710,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127412342</v>
+        <v>127412339</v>
       </c>
       <c r="B47" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>692822</v>
+        <v>692742</v>
       </c>
       <c r="R47" t="n">
-        <v>7149491</v>
+        <v>7149553</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5816,10 +5816,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127412339</v>
+        <v>127412342</v>
       </c>
       <c r="B48" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5855,10 +5855,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>692742</v>
+        <v>692822</v>
       </c>
       <c r="R48" t="n">
-        <v>7149553</v>
+        <v>7149491</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5925,7 +5925,7 @@
         <v>127412349</v>
       </c>
       <c r="B49" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>127412320</v>
       </c>
       <c r="B50" t="n">
-        <v>92642</v>
+        <v>92646</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>127412352</v>
       </c>
       <c r="B51" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>127412341</v>
       </c>
       <c r="B52" t="n">
-        <v>92610</v>
+        <v>92614</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>127412359</v>
       </c>
       <c r="B53" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6452,32 +6452,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127412366</v>
+        <v>127412338</v>
       </c>
       <c r="B54" t="n">
-        <v>92632</v>
+        <v>92620</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>693119</v>
+        <v>692701</v>
       </c>
       <c r="R54" t="n">
-        <v>7149224</v>
+        <v>7149567</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6558,32 +6558,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412338</v>
+        <v>127412366</v>
       </c>
       <c r="B55" t="n">
-        <v>92616</v>
+        <v>92636</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6597,10 +6597,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>692701</v>
+        <v>693119</v>
       </c>
       <c r="R55" t="n">
-        <v>7149567</v>
+        <v>7149224</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6667,7 +6667,7 @@
         <v>127412323</v>
       </c>
       <c r="B56" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6770,10 +6770,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127412325</v>
+        <v>127412361</v>
       </c>
       <c r="B57" t="n">
-        <v>92632</v>
+        <v>92636</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6809,10 +6809,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>692939</v>
+        <v>693017</v>
       </c>
       <c r="R57" t="n">
-        <v>7149230</v>
+        <v>7149215</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6876,10 +6876,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127412361</v>
+        <v>127412325</v>
       </c>
       <c r="B58" t="n">
-        <v>92632</v>
+        <v>92636</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>693017</v>
+        <v>692939</v>
       </c>
       <c r="R58" t="n">
-        <v>7149215</v>
+        <v>7149230</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6985,7 +6985,7 @@
         <v>127412347</v>
       </c>
       <c r="B59" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7088,32 +7088,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412331</v>
+        <v>127412364</v>
       </c>
       <c r="B60" t="n">
-        <v>92616</v>
+        <v>92636</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7127,10 +7127,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>692989</v>
+        <v>693060</v>
       </c>
       <c r="R60" t="n">
-        <v>7149194</v>
+        <v>7149216</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7194,32 +7194,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412370</v>
+        <v>127412333</v>
       </c>
       <c r="B61" t="n">
-        <v>92616</v>
+        <v>92612</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7233,10 +7233,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>693118</v>
+        <v>692649</v>
       </c>
       <c r="R61" t="n">
-        <v>7149155</v>
+        <v>7149598</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7300,32 +7300,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127412364</v>
+        <v>127412362</v>
       </c>
       <c r="B62" t="n">
-        <v>92632</v>
+        <v>92620</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>693060</v>
+        <v>693013</v>
       </c>
       <c r="R62" t="n">
-        <v>7149216</v>
+        <v>7149208</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7406,32 +7406,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127412333</v>
+        <v>127412331</v>
       </c>
       <c r="B63" t="n">
-        <v>92608</v>
+        <v>92620</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>692649</v>
+        <v>692989</v>
       </c>
       <c r="R63" t="n">
-        <v>7149598</v>
+        <v>7149194</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7515,7 +7515,7 @@
         <v>127412344</v>
       </c>
       <c r="B64" t="n">
-        <v>92628</v>
+        <v>92632</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7618,10 +7618,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412362</v>
+        <v>127412370</v>
       </c>
       <c r="B65" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7657,10 +7657,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>693013</v>
+        <v>693118</v>
       </c>
       <c r="R65" t="n">
-        <v>7149208</v>
+        <v>7149155</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7727,7 +7727,7 @@
         <v>127412345</v>
       </c>
       <c r="B66" t="n">
-        <v>92644</v>
+        <v>92648</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>127412356</v>
       </c>
       <c r="B67" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7936,32 +7936,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127412353</v>
+        <v>127412355</v>
       </c>
       <c r="B68" t="n">
-        <v>78773</v>
+        <v>92620</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7975,10 +7975,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>692989</v>
+        <v>692985</v>
       </c>
       <c r="R68" t="n">
-        <v>7149374</v>
+        <v>7149369</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8042,32 +8042,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127412357</v>
+        <v>127412350</v>
       </c>
       <c r="B69" t="n">
-        <v>92644</v>
+        <v>92632</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -8081,10 +8081,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>692963</v>
+        <v>692958</v>
       </c>
       <c r="R69" t="n">
-        <v>7149329</v>
+        <v>7149383</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8148,32 +8148,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127412350</v>
+        <v>127412357</v>
       </c>
       <c r="B70" t="n">
-        <v>92628</v>
+        <v>92648</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>692958</v>
+        <v>692963</v>
       </c>
       <c r="R70" t="n">
-        <v>7149383</v>
+        <v>7149329</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8254,32 +8254,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127412355</v>
+        <v>127412353</v>
       </c>
       <c r="B71" t="n">
-        <v>92616</v>
+        <v>78777</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8293,10 +8293,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>692985</v>
+        <v>692989</v>
       </c>
       <c r="R71" t="n">
-        <v>7149369</v>
+        <v>7149374</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8363,7 +8363,7 @@
         <v>127412340</v>
       </c>
       <c r="B72" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 52547-2020 artfynd.xlsx
+++ b/artfynd/A 52547-2020 artfynd.xlsx
@@ -3590,10 +3590,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127412326</v>
+        <v>127412328</v>
       </c>
       <c r="B27" t="n">
-        <v>92636</v>
+        <v>92656</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3601,21 +3601,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>692934</v>
+        <v>692931</v>
       </c>
       <c r="R27" t="n">
-        <v>7149219</v>
+        <v>7149192</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3696,7 +3696,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127412327</v>
+        <v>127412332</v>
       </c>
       <c r="B28" t="n">
         <v>92632</v>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>692929</v>
+        <v>692625</v>
       </c>
       <c r="R28" t="n">
-        <v>7149201</v>
+        <v>7149521</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4014,32 +4014,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127412332</v>
+        <v>127412326</v>
       </c>
       <c r="B31" t="n">
-        <v>92632</v>
+        <v>92636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>692625</v>
+        <v>692934</v>
       </c>
       <c r="R31" t="n">
-        <v>7149521</v>
+        <v>7149219</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4120,32 +4120,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127412328</v>
+        <v>127412327</v>
       </c>
       <c r="B32" t="n">
-        <v>92656</v>
+        <v>92632</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>692931</v>
+        <v>692929</v>
       </c>
       <c r="R32" t="n">
-        <v>7149192</v>
+        <v>7149201</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4968,10 +4968,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127412330</v>
+        <v>127412351</v>
       </c>
       <c r="B40" t="n">
-        <v>92656</v>
+        <v>79607</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4979,21 +4979,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>692974</v>
+        <v>692985</v>
       </c>
       <c r="R40" t="n">
-        <v>7149201</v>
+        <v>7149378</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5074,10 +5074,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127412351</v>
+        <v>127412330</v>
       </c>
       <c r="B41" t="n">
-        <v>79607</v>
+        <v>92656</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>692985</v>
+        <v>692974</v>
       </c>
       <c r="R41" t="n">
-        <v>7149378</v>
+        <v>7149201</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5710,7 +5710,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127412339</v>
+        <v>127412342</v>
       </c>
       <c r="B47" t="n">
         <v>92620</v>
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>692742</v>
+        <v>692822</v>
       </c>
       <c r="R47" t="n">
-        <v>7149553</v>
+        <v>7149491</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5816,7 +5816,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127412342</v>
+        <v>127412339</v>
       </c>
       <c r="B48" t="n">
         <v>92620</v>
@@ -5855,10 +5855,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>692822</v>
+        <v>692742</v>
       </c>
       <c r="R48" t="n">
-        <v>7149491</v>
+        <v>7149553</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6028,10 +6028,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127412320</v>
+        <v>127412352</v>
       </c>
       <c r="B50" t="n">
-        <v>92646</v>
+        <v>79636</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5448</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>692916</v>
+        <v>692989</v>
       </c>
       <c r="R50" t="n">
-        <v>7149304</v>
+        <v>7149374</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6134,10 +6134,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127412352</v>
+        <v>127412320</v>
       </c>
       <c r="B51" t="n">
-        <v>79636</v>
+        <v>92646</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>5448</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>692989</v>
+        <v>692916</v>
       </c>
       <c r="R51" t="n">
-        <v>7149374</v>
+        <v>7149304</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6452,32 +6452,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127412338</v>
+        <v>127412366</v>
       </c>
       <c r="B54" t="n">
-        <v>92620</v>
+        <v>92636</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>692701</v>
+        <v>693119</v>
       </c>
       <c r="R54" t="n">
-        <v>7149567</v>
+        <v>7149224</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6558,32 +6558,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412366</v>
+        <v>127412338</v>
       </c>
       <c r="B55" t="n">
-        <v>92636</v>
+        <v>92620</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6597,10 +6597,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>693119</v>
+        <v>692701</v>
       </c>
       <c r="R55" t="n">
-        <v>7149224</v>
+        <v>7149567</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6770,7 +6770,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127412361</v>
+        <v>127412325</v>
       </c>
       <c r="B57" t="n">
         <v>92636</v>
@@ -6809,10 +6809,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>693017</v>
+        <v>692939</v>
       </c>
       <c r="R57" t="n">
-        <v>7149215</v>
+        <v>7149230</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6876,7 +6876,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127412325</v>
+        <v>127412361</v>
       </c>
       <c r="B58" t="n">
         <v>92636</v>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>692939</v>
+        <v>693017</v>
       </c>
       <c r="R58" t="n">
-        <v>7149230</v>
+        <v>7149215</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7088,10 +7088,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412364</v>
+        <v>127412345</v>
       </c>
       <c r="B60" t="n">
-        <v>92636</v>
+        <v>92648</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7127,10 +7127,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>693060</v>
+        <v>692899</v>
       </c>
       <c r="R60" t="n">
-        <v>7149216</v>
+        <v>7149426</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7194,32 +7194,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412333</v>
+        <v>127412331</v>
       </c>
       <c r="B61" t="n">
-        <v>92612</v>
+        <v>92620</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7233,10 +7233,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>692649</v>
+        <v>692989</v>
       </c>
       <c r="R61" t="n">
-        <v>7149598</v>
+        <v>7149194</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7300,7 +7300,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127412362</v>
+        <v>127412370</v>
       </c>
       <c r="B62" t="n">
         <v>92620</v>
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>693013</v>
+        <v>693118</v>
       </c>
       <c r="R62" t="n">
-        <v>7149208</v>
+        <v>7149155</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7406,32 +7406,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127412331</v>
+        <v>127412364</v>
       </c>
       <c r="B63" t="n">
-        <v>92620</v>
+        <v>92636</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>692989</v>
+        <v>693060</v>
       </c>
       <c r="R63" t="n">
-        <v>7149194</v>
+        <v>7149216</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7512,32 +7512,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127412344</v>
+        <v>127412333</v>
       </c>
       <c r="B64" t="n">
-        <v>92632</v>
+        <v>92612</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>692854</v>
+        <v>692649</v>
       </c>
       <c r="R64" t="n">
-        <v>7149427</v>
+        <v>7149598</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7618,10 +7618,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412370</v>
+        <v>127412344</v>
       </c>
       <c r="B65" t="n">
-        <v>92620</v>
+        <v>92632</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7629,21 +7629,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7657,10 +7657,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>693118</v>
+        <v>692854</v>
       </c>
       <c r="R65" t="n">
-        <v>7149155</v>
+        <v>7149427</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7724,32 +7724,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127412345</v>
+        <v>127412362</v>
       </c>
       <c r="B66" t="n">
-        <v>92648</v>
+        <v>92620</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>692899</v>
+        <v>693013</v>
       </c>
       <c r="R66" t="n">
-        <v>7149426</v>
+        <v>7149208</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7936,10 +7936,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127412355</v>
+        <v>127412350</v>
       </c>
       <c r="B68" t="n">
-        <v>92620</v>
+        <v>92632</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7947,21 +7947,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7975,10 +7975,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>692985</v>
+        <v>692958</v>
       </c>
       <c r="R68" t="n">
-        <v>7149369</v>
+        <v>7149383</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8042,10 +8042,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127412350</v>
+        <v>127412355</v>
       </c>
       <c r="B69" t="n">
-        <v>92632</v>
+        <v>92620</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8053,21 +8053,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -8081,10 +8081,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>692958</v>
+        <v>692985</v>
       </c>
       <c r="R69" t="n">
-        <v>7149383</v>
+        <v>7149369</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>

--- a/artfynd/A 52547-2020 artfynd.xlsx
+++ b/artfynd/A 52547-2020 artfynd.xlsx
@@ -4544,32 +4544,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127412324</v>
+        <v>127412360</v>
       </c>
       <c r="B36" t="n">
-        <v>92608</v>
+        <v>92636</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>149</v>
+        <v>2059</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>692937</v>
+        <v>692978</v>
       </c>
       <c r="R36" t="n">
-        <v>7149228</v>
+        <v>7149291</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127412360</v>
+        <v>127412324</v>
       </c>
       <c r="B37" t="n">
-        <v>92636</v>
+        <v>92608</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2059</v>
+        <v>149</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>692978</v>
+        <v>692937</v>
       </c>
       <c r="R37" t="n">
-        <v>7149291</v>
+        <v>7149228</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5286,10 +5286,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127412346</v>
+        <v>127412368</v>
       </c>
       <c r="B43" t="n">
-        <v>92620</v>
+        <v>92632</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5297,21 +5297,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>692896</v>
+        <v>693101</v>
       </c>
       <c r="R43" t="n">
-        <v>7149409</v>
+        <v>7149176</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5392,10 +5392,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127412368</v>
+        <v>127412358</v>
       </c>
       <c r="B44" t="n">
-        <v>92632</v>
+        <v>92620</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5403,21 +5403,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>693101</v>
+        <v>692977</v>
       </c>
       <c r="R44" t="n">
-        <v>7149176</v>
+        <v>7149327</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5498,32 +5498,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127412358</v>
+        <v>127412348</v>
       </c>
       <c r="B45" t="n">
-        <v>92620</v>
+        <v>5493</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>692977</v>
+        <v>692895</v>
       </c>
       <c r="R45" t="n">
-        <v>7149327</v>
+        <v>7149371</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5604,32 +5604,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127412348</v>
+        <v>127412346</v>
       </c>
       <c r="B46" t="n">
-        <v>5493</v>
+        <v>92620</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5643,10 +5643,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>692895</v>
+        <v>692896</v>
       </c>
       <c r="R46" t="n">
-        <v>7149371</v>
+        <v>7149409</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>

--- a/artfynd/A 52547-2020 artfynd.xlsx
+++ b/artfynd/A 52547-2020 artfynd.xlsx
@@ -5286,10 +5286,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127412368</v>
+        <v>127412346</v>
       </c>
       <c r="B43" t="n">
-        <v>92632</v>
+        <v>92620</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5297,21 +5297,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>693101</v>
+        <v>692896</v>
       </c>
       <c r="R43" t="n">
-        <v>7149176</v>
+        <v>7149409</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5392,10 +5392,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127412358</v>
+        <v>127412368</v>
       </c>
       <c r="B44" t="n">
-        <v>92620</v>
+        <v>92632</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5403,21 +5403,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>692977</v>
+        <v>693101</v>
       </c>
       <c r="R44" t="n">
-        <v>7149327</v>
+        <v>7149176</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5498,32 +5498,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127412348</v>
+        <v>127412358</v>
       </c>
       <c r="B45" t="n">
-        <v>5493</v>
+        <v>92620</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>692895</v>
+        <v>692977</v>
       </c>
       <c r="R45" t="n">
-        <v>7149371</v>
+        <v>7149327</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5604,32 +5604,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127412346</v>
+        <v>127412348</v>
       </c>
       <c r="B46" t="n">
-        <v>92620</v>
+        <v>5493</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5643,10 +5643,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>692896</v>
+        <v>692895</v>
       </c>
       <c r="R46" t="n">
-        <v>7149409</v>
+        <v>7149371</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>

--- a/artfynd/A 52547-2020 artfynd.xlsx
+++ b/artfynd/A 52547-2020 artfynd.xlsx
@@ -3590,32 +3590,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127412328</v>
+        <v>127412327</v>
       </c>
       <c r="B27" t="n">
-        <v>92656</v>
+        <v>92632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>692931</v>
+        <v>692929</v>
       </c>
       <c r="R27" t="n">
-        <v>7149192</v>
+        <v>7149201</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127412332</v>
+        <v>127412329</v>
       </c>
       <c r="B28" t="n">
-        <v>92632</v>
+        <v>92620</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>692625</v>
+        <v>692950</v>
       </c>
       <c r="R28" t="n">
-        <v>7149521</v>
+        <v>7149192</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3802,7 +3802,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127412329</v>
+        <v>127412322</v>
       </c>
       <c r="B29" t="n">
         <v>92620</v>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>692950</v>
+        <v>692932</v>
       </c>
       <c r="R29" t="n">
-        <v>7149192</v>
+        <v>7149288</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3908,10 +3908,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127412322</v>
+        <v>127412332</v>
       </c>
       <c r="B30" t="n">
-        <v>92620</v>
+        <v>92632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3919,21 +3919,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>692932</v>
+        <v>692625</v>
       </c>
       <c r="R30" t="n">
-        <v>7149288</v>
+        <v>7149521</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4120,32 +4120,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127412327</v>
+        <v>127412328</v>
       </c>
       <c r="B32" t="n">
-        <v>92632</v>
+        <v>92656</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>692929</v>
+        <v>692931</v>
       </c>
       <c r="R32" t="n">
-        <v>7149201</v>
+        <v>7149192</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4226,32 +4226,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127412363</v>
+        <v>127412334</v>
       </c>
       <c r="B33" t="n">
-        <v>92620</v>
+        <v>5493</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4265,10 +4265,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>693054</v>
+        <v>692673</v>
       </c>
       <c r="R33" t="n">
-        <v>7149264</v>
+        <v>7149439</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4332,7 +4332,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127412365</v>
+        <v>127412363</v>
       </c>
       <c r="B34" t="n">
         <v>92620</v>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>693089</v>
+        <v>693054</v>
       </c>
       <c r="R34" t="n">
-        <v>7149223</v>
+        <v>7149264</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4438,32 +4438,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127412334</v>
+        <v>127412365</v>
       </c>
       <c r="B35" t="n">
-        <v>5493</v>
+        <v>92620</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>692673</v>
+        <v>693089</v>
       </c>
       <c r="R35" t="n">
-        <v>7149439</v>
+        <v>7149223</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4544,32 +4544,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127412360</v>
+        <v>127412324</v>
       </c>
       <c r="B36" t="n">
-        <v>92636</v>
+        <v>92608</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2059</v>
+        <v>149</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>692978</v>
+        <v>692937</v>
       </c>
       <c r="R36" t="n">
-        <v>7149291</v>
+        <v>7149228</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127412324</v>
+        <v>127412360</v>
       </c>
       <c r="B37" t="n">
-        <v>92608</v>
+        <v>92636</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>149</v>
+        <v>2059</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>692937</v>
+        <v>692978</v>
       </c>
       <c r="R37" t="n">
-        <v>7149228</v>
+        <v>7149291</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4968,10 +4968,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127412351</v>
+        <v>127412330</v>
       </c>
       <c r="B40" t="n">
-        <v>79607</v>
+        <v>92656</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4979,21 +4979,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>692985</v>
+        <v>692974</v>
       </c>
       <c r="R40" t="n">
-        <v>7149378</v>
+        <v>7149201</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5074,10 +5074,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127412330</v>
+        <v>127412351</v>
       </c>
       <c r="B41" t="n">
-        <v>92656</v>
+        <v>79607</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>692974</v>
+        <v>692985</v>
       </c>
       <c r="R41" t="n">
-        <v>7149201</v>
+        <v>7149378</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5710,7 +5710,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127412342</v>
+        <v>127412339</v>
       </c>
       <c r="B47" t="n">
         <v>92620</v>
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>692822</v>
+        <v>692742</v>
       </c>
       <c r="R47" t="n">
-        <v>7149491</v>
+        <v>7149553</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5816,7 +5816,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127412339</v>
+        <v>127412342</v>
       </c>
       <c r="B48" t="n">
         <v>92620</v>
@@ -5855,10 +5855,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>692742</v>
+        <v>692822</v>
       </c>
       <c r="R48" t="n">
-        <v>7149553</v>
+        <v>7149491</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6028,10 +6028,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127412352</v>
+        <v>127412320</v>
       </c>
       <c r="B50" t="n">
-        <v>79636</v>
+        <v>92646</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>5448</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>692989</v>
+        <v>692916</v>
       </c>
       <c r="R50" t="n">
-        <v>7149374</v>
+        <v>7149304</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6134,10 +6134,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127412320</v>
+        <v>127412352</v>
       </c>
       <c r="B51" t="n">
-        <v>92646</v>
+        <v>79636</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5448</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>692916</v>
+        <v>692989</v>
       </c>
       <c r="R51" t="n">
-        <v>7149304</v>
+        <v>7149374</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -7088,10 +7088,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412345</v>
+        <v>127412364</v>
       </c>
       <c r="B60" t="n">
-        <v>92648</v>
+        <v>92636</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7127,10 +7127,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>692899</v>
+        <v>693060</v>
       </c>
       <c r="R60" t="n">
-        <v>7149426</v>
+        <v>7149216</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7194,7 +7194,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412331</v>
+        <v>127412362</v>
       </c>
       <c r="B61" t="n">
         <v>92620</v>
@@ -7233,10 +7233,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>692989</v>
+        <v>693013</v>
       </c>
       <c r="R61" t="n">
-        <v>7149194</v>
+        <v>7149208</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7300,7 +7300,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127412370</v>
+        <v>127412331</v>
       </c>
       <c r="B62" t="n">
         <v>92620</v>
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>693118</v>
+        <v>692989</v>
       </c>
       <c r="R62" t="n">
-        <v>7149155</v>
+        <v>7149194</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7406,10 +7406,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127412364</v>
+        <v>127412345</v>
       </c>
       <c r="B63" t="n">
-        <v>92636</v>
+        <v>92648</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7417,21 +7417,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>693060</v>
+        <v>692899</v>
       </c>
       <c r="R63" t="n">
-        <v>7149216</v>
+        <v>7149426</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7512,32 +7512,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127412333</v>
+        <v>127412344</v>
       </c>
       <c r="B64" t="n">
-        <v>92612</v>
+        <v>92632</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>692649</v>
+        <v>692854</v>
       </c>
       <c r="R64" t="n">
-        <v>7149598</v>
+        <v>7149427</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7618,10 +7618,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412344</v>
+        <v>127412370</v>
       </c>
       <c r="B65" t="n">
-        <v>92632</v>
+        <v>92620</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7629,21 +7629,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7657,10 +7657,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>692854</v>
+        <v>693118</v>
       </c>
       <c r="R65" t="n">
-        <v>7149427</v>
+        <v>7149155</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7724,32 +7724,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127412362</v>
+        <v>127412333</v>
       </c>
       <c r="B66" t="n">
-        <v>92620</v>
+        <v>92612</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>693013</v>
+        <v>692649</v>
       </c>
       <c r="R66" t="n">
-        <v>7149208</v>
+        <v>7149598</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7936,32 +7936,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127412350</v>
+        <v>127412357</v>
       </c>
       <c r="B68" t="n">
-        <v>92632</v>
+        <v>92648</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7975,10 +7975,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>692958</v>
+        <v>692963</v>
       </c>
       <c r="R68" t="n">
-        <v>7149383</v>
+        <v>7149329</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8148,32 +8148,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127412357</v>
+        <v>127412350</v>
       </c>
       <c r="B70" t="n">
-        <v>92648</v>
+        <v>92632</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>692963</v>
+        <v>692958</v>
       </c>
       <c r="R70" t="n">
-        <v>7149329</v>
+        <v>7149383</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>

--- a/artfynd/A 52547-2020 artfynd.xlsx
+++ b/artfynd/A 52547-2020 artfynd.xlsx
@@ -3590,32 +3590,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127412327</v>
+        <v>127412326</v>
       </c>
       <c r="B27" t="n">
-        <v>92632</v>
+        <v>92636</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>692929</v>
+        <v>692934</v>
       </c>
       <c r="R27" t="n">
-        <v>7149201</v>
+        <v>7149219</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127412329</v>
+        <v>127412327</v>
       </c>
       <c r="B28" t="n">
-        <v>92620</v>
+        <v>92632</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>692950</v>
+        <v>692929</v>
       </c>
       <c r="R28" t="n">
-        <v>7149192</v>
+        <v>7149201</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3802,7 +3802,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127412322</v>
+        <v>127412329</v>
       </c>
       <c r="B29" t="n">
         <v>92620</v>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>692932</v>
+        <v>692950</v>
       </c>
       <c r="R29" t="n">
-        <v>7149288</v>
+        <v>7149192</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3908,10 +3908,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127412332</v>
+        <v>127412322</v>
       </c>
       <c r="B30" t="n">
-        <v>92632</v>
+        <v>92620</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3919,21 +3919,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>692625</v>
+        <v>692932</v>
       </c>
       <c r="R30" t="n">
-        <v>7149521</v>
+        <v>7149288</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4014,32 +4014,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127412326</v>
+        <v>127412332</v>
       </c>
       <c r="B31" t="n">
-        <v>92636</v>
+        <v>92632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>692934</v>
+        <v>692625</v>
       </c>
       <c r="R31" t="n">
-        <v>7149219</v>
+        <v>7149521</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4226,32 +4226,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127412334</v>
+        <v>127412363</v>
       </c>
       <c r="B33" t="n">
-        <v>5493</v>
+        <v>92620</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4265,10 +4265,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>692673</v>
+        <v>693054</v>
       </c>
       <c r="R33" t="n">
-        <v>7149439</v>
+        <v>7149264</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4332,7 +4332,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127412363</v>
+        <v>127412365</v>
       </c>
       <c r="B34" t="n">
         <v>92620</v>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>693054</v>
+        <v>693089</v>
       </c>
       <c r="R34" t="n">
-        <v>7149264</v>
+        <v>7149223</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4438,32 +4438,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127412365</v>
+        <v>127412334</v>
       </c>
       <c r="B35" t="n">
-        <v>92620</v>
+        <v>5493</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>693089</v>
+        <v>692673</v>
       </c>
       <c r="R35" t="n">
-        <v>7149223</v>
+        <v>7149439</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4756,32 +4756,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127412367</v>
+        <v>127412321</v>
       </c>
       <c r="B38" t="n">
-        <v>92620</v>
+        <v>92614</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>693081</v>
+        <v>692916</v>
       </c>
       <c r="R38" t="n">
-        <v>7149184</v>
+        <v>7149304</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4862,10 +4862,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127412321</v>
+        <v>127412330</v>
       </c>
       <c r="B39" t="n">
-        <v>92614</v>
+        <v>92656</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4873,21 +4873,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>692916</v>
+        <v>692974</v>
       </c>
       <c r="R39" t="n">
-        <v>7149304</v>
+        <v>7149201</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4968,10 +4968,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127412330</v>
+        <v>127412351</v>
       </c>
       <c r="B40" t="n">
-        <v>92656</v>
+        <v>79607</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4979,21 +4979,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>692974</v>
+        <v>692985</v>
       </c>
       <c r="R40" t="n">
-        <v>7149201</v>
+        <v>7149378</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5074,32 +5074,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127412351</v>
+        <v>127412367</v>
       </c>
       <c r="B41" t="n">
-        <v>79607</v>
+        <v>92620</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>692985</v>
+        <v>693081</v>
       </c>
       <c r="R41" t="n">
-        <v>7149378</v>
+        <v>7149184</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -7936,10 +7936,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127412357</v>
+        <v>127412353</v>
       </c>
       <c r="B68" t="n">
-        <v>92648</v>
+        <v>78777</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7947,21 +7947,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7975,10 +7975,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>692963</v>
+        <v>692989</v>
       </c>
       <c r="R68" t="n">
-        <v>7149329</v>
+        <v>7149374</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8042,32 +8042,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127412355</v>
+        <v>127412357</v>
       </c>
       <c r="B69" t="n">
-        <v>92620</v>
+        <v>92648</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -8081,10 +8081,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>692985</v>
+        <v>692963</v>
       </c>
       <c r="R69" t="n">
-        <v>7149369</v>
+        <v>7149329</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8148,10 +8148,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127412350</v>
+        <v>127412355</v>
       </c>
       <c r="B70" t="n">
-        <v>92632</v>
+        <v>92620</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8159,21 +8159,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>692958</v>
+        <v>692985</v>
       </c>
       <c r="R70" t="n">
-        <v>7149383</v>
+        <v>7149369</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8254,32 +8254,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127412353</v>
+        <v>127412350</v>
       </c>
       <c r="B71" t="n">
-        <v>78777</v>
+        <v>92632</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8293,10 +8293,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>692989</v>
+        <v>692958</v>
       </c>
       <c r="R71" t="n">
-        <v>7149374</v>
+        <v>7149383</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>

--- a/artfynd/A 52547-2020 artfynd.xlsx
+++ b/artfynd/A 52547-2020 artfynd.xlsx
@@ -3590,32 +3590,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127412326</v>
+        <v>127412332</v>
       </c>
       <c r="B27" t="n">
-        <v>92636</v>
+        <v>92634</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>692934</v>
+        <v>692625</v>
       </c>
       <c r="R27" t="n">
-        <v>7149219</v>
+        <v>7149521</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127412327</v>
+        <v>127412329</v>
       </c>
       <c r="B28" t="n">
-        <v>92632</v>
+        <v>92622</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>692929</v>
+        <v>692950</v>
       </c>
       <c r="R28" t="n">
-        <v>7149201</v>
+        <v>7149192</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3802,10 +3802,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127412329</v>
+        <v>127412322</v>
       </c>
       <c r="B29" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>692950</v>
+        <v>692932</v>
       </c>
       <c r="R29" t="n">
-        <v>7149192</v>
+        <v>7149288</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3908,32 +3908,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127412322</v>
+        <v>127412326</v>
       </c>
       <c r="B30" t="n">
-        <v>92620</v>
+        <v>92638</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>692932</v>
+        <v>692934</v>
       </c>
       <c r="R30" t="n">
-        <v>7149288</v>
+        <v>7149219</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127412332</v>
+        <v>127412327</v>
       </c>
       <c r="B31" t="n">
-        <v>92632</v>
+        <v>92634</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>692625</v>
+        <v>692929</v>
       </c>
       <c r="R31" t="n">
-        <v>7149521</v>
+        <v>7149201</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4123,7 +4123,7 @@
         <v>127412328</v>
       </c>
       <c r="B32" t="n">
-        <v>92656</v>
+        <v>92658</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>127412363</v>
       </c>
       <c r="B33" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>127412365</v>
       </c>
       <c r="B34" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4544,32 +4544,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127412324</v>
+        <v>127412360</v>
       </c>
       <c r="B36" t="n">
-        <v>92608</v>
+        <v>92638</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>149</v>
+        <v>2059</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>692937</v>
+        <v>692978</v>
       </c>
       <c r="R36" t="n">
-        <v>7149228</v>
+        <v>7149291</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127412360</v>
+        <v>127412324</v>
       </c>
       <c r="B37" t="n">
-        <v>92636</v>
+        <v>92610</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2059</v>
+        <v>149</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>692978</v>
+        <v>692937</v>
       </c>
       <c r="R37" t="n">
-        <v>7149291</v>
+        <v>7149228</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4756,32 +4756,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127412321</v>
+        <v>127412367</v>
       </c>
       <c r="B38" t="n">
-        <v>92614</v>
+        <v>92622</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>692916</v>
+        <v>693081</v>
       </c>
       <c r="R38" t="n">
-        <v>7149304</v>
+        <v>7149184</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4862,10 +4862,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127412330</v>
+        <v>127412321</v>
       </c>
       <c r="B39" t="n">
-        <v>92656</v>
+        <v>92616</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4873,21 +4873,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>692974</v>
+        <v>692916</v>
       </c>
       <c r="R39" t="n">
-        <v>7149201</v>
+        <v>7149304</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4968,10 +4968,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127412351</v>
+        <v>127412330</v>
       </c>
       <c r="B40" t="n">
-        <v>79607</v>
+        <v>92658</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4979,21 +4979,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>692985</v>
+        <v>692974</v>
       </c>
       <c r="R40" t="n">
-        <v>7149378</v>
+        <v>7149201</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5074,32 +5074,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127412367</v>
+        <v>127412351</v>
       </c>
       <c r="B41" t="n">
-        <v>92620</v>
+        <v>79609</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>693081</v>
+        <v>692985</v>
       </c>
       <c r="R41" t="n">
-        <v>7149184</v>
+        <v>7149378</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5183,7 +5183,7 @@
         <v>127412343</v>
       </c>
       <c r="B42" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>127412346</v>
       </c>
       <c r="B43" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>127412368</v>
       </c>
       <c r="B44" t="n">
-        <v>92632</v>
+        <v>92634</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>127412358</v>
       </c>
       <c r="B45" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5710,10 +5710,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127412339</v>
+        <v>127412342</v>
       </c>
       <c r="B47" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>692742</v>
+        <v>692822</v>
       </c>
       <c r="R47" t="n">
-        <v>7149553</v>
+        <v>7149491</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5816,10 +5816,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127412342</v>
+        <v>127412339</v>
       </c>
       <c r="B48" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5855,10 +5855,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>692822</v>
+        <v>692742</v>
       </c>
       <c r="R48" t="n">
-        <v>7149491</v>
+        <v>7149553</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5925,7 +5925,7 @@
         <v>127412349</v>
       </c>
       <c r="B49" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6028,10 +6028,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127412320</v>
+        <v>127412352</v>
       </c>
       <c r="B50" t="n">
-        <v>92646</v>
+        <v>79638</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5448</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>692916</v>
+        <v>692989</v>
       </c>
       <c r="R50" t="n">
-        <v>7149304</v>
+        <v>7149374</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6134,10 +6134,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127412352</v>
+        <v>127412320</v>
       </c>
       <c r="B51" t="n">
-        <v>79636</v>
+        <v>92648</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>5448</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>692989</v>
+        <v>692916</v>
       </c>
       <c r="R51" t="n">
-        <v>7149374</v>
+        <v>7149304</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6243,7 +6243,7 @@
         <v>127412341</v>
       </c>
       <c r="B52" t="n">
-        <v>92614</v>
+        <v>92616</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>127412359</v>
       </c>
       <c r="B53" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>127412366</v>
       </c>
       <c r="B54" t="n">
-        <v>92636</v>
+        <v>92638</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>127412338</v>
       </c>
       <c r="B55" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>127412323</v>
       </c>
       <c r="B56" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>127412325</v>
       </c>
       <c r="B57" t="n">
-        <v>92636</v>
+        <v>92638</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>127412361</v>
       </c>
       <c r="B58" t="n">
-        <v>92636</v>
+        <v>92638</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>127412347</v>
       </c>
       <c r="B59" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7088,32 +7088,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412364</v>
+        <v>127412331</v>
       </c>
       <c r="B60" t="n">
-        <v>92636</v>
+        <v>92622</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7127,10 +7127,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>693060</v>
+        <v>692989</v>
       </c>
       <c r="R60" t="n">
-        <v>7149216</v>
+        <v>7149194</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7194,10 +7194,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412362</v>
+        <v>127412370</v>
       </c>
       <c r="B61" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7233,10 +7233,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>693013</v>
+        <v>693118</v>
       </c>
       <c r="R61" t="n">
-        <v>7149208</v>
+        <v>7149155</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7300,32 +7300,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127412331</v>
+        <v>127412364</v>
       </c>
       <c r="B62" t="n">
-        <v>92620</v>
+        <v>92638</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>692989</v>
+        <v>693060</v>
       </c>
       <c r="R62" t="n">
-        <v>7149194</v>
+        <v>7149216</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7406,10 +7406,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127412345</v>
+        <v>127412333</v>
       </c>
       <c r="B63" t="n">
-        <v>92648</v>
+        <v>92614</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7417,21 +7417,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>692899</v>
+        <v>692649</v>
       </c>
       <c r="R63" t="n">
-        <v>7149426</v>
+        <v>7149598</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7515,7 +7515,7 @@
         <v>127412344</v>
       </c>
       <c r="B64" t="n">
-        <v>92632</v>
+        <v>92634</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7618,10 +7618,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412370</v>
+        <v>127412362</v>
       </c>
       <c r="B65" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7657,10 +7657,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>693118</v>
+        <v>693013</v>
       </c>
       <c r="R65" t="n">
-        <v>7149155</v>
+        <v>7149208</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7724,10 +7724,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127412333</v>
+        <v>127412345</v>
       </c>
       <c r="B66" t="n">
-        <v>92612</v>
+        <v>92650</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7735,21 +7735,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>692649</v>
+        <v>692899</v>
       </c>
       <c r="R66" t="n">
-        <v>7149598</v>
+        <v>7149426</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7833,7 +7833,7 @@
         <v>127412356</v>
       </c>
       <c r="B67" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7936,32 +7936,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127412353</v>
+        <v>127412350</v>
       </c>
       <c r="B68" t="n">
-        <v>78777</v>
+        <v>92634</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7975,10 +7975,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>692989</v>
+        <v>692958</v>
       </c>
       <c r="R68" t="n">
-        <v>7149374</v>
+        <v>7149383</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8042,32 +8042,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127412357</v>
+        <v>127412355</v>
       </c>
       <c r="B69" t="n">
-        <v>92648</v>
+        <v>92622</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -8081,10 +8081,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>692963</v>
+        <v>692985</v>
       </c>
       <c r="R69" t="n">
-        <v>7149329</v>
+        <v>7149369</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8148,32 +8148,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127412355</v>
+        <v>127412357</v>
       </c>
       <c r="B70" t="n">
-        <v>92620</v>
+        <v>92650</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>692985</v>
+        <v>692963</v>
       </c>
       <c r="R70" t="n">
-        <v>7149369</v>
+        <v>7149329</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8254,32 +8254,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127412350</v>
+        <v>127412353</v>
       </c>
       <c r="B71" t="n">
-        <v>92632</v>
+        <v>78779</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8293,10 +8293,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>692958</v>
+        <v>692989</v>
       </c>
       <c r="R71" t="n">
-        <v>7149383</v>
+        <v>7149374</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8363,7 +8363,7 @@
         <v>127412340</v>
       </c>
       <c r="B72" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 52547-2020 artfynd.xlsx
+++ b/artfynd/A 52547-2020 artfynd.xlsx
@@ -3590,7 +3590,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127412332</v>
+        <v>127412327</v>
       </c>
       <c r="B27" t="n">
         <v>92634</v>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>692625</v>
+        <v>692929</v>
       </c>
       <c r="R27" t="n">
-        <v>7149521</v>
+        <v>7149201</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3908,32 +3908,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127412326</v>
+        <v>127412332</v>
       </c>
       <c r="B30" t="n">
-        <v>92638</v>
+        <v>92634</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>692934</v>
+        <v>692625</v>
       </c>
       <c r="R30" t="n">
-        <v>7149219</v>
+        <v>7149521</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4014,32 +4014,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127412327</v>
+        <v>127412328</v>
       </c>
       <c r="B31" t="n">
-        <v>92634</v>
+        <v>92658</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>692929</v>
+        <v>692931</v>
       </c>
       <c r="R31" t="n">
-        <v>7149201</v>
+        <v>7149192</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4120,10 +4120,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127412328</v>
+        <v>127412326</v>
       </c>
       <c r="B32" t="n">
-        <v>92658</v>
+        <v>92638</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4131,21 +4131,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>692931</v>
+        <v>692934</v>
       </c>
       <c r="R32" t="n">
-        <v>7149192</v>
+        <v>7149219</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4226,32 +4226,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127412363</v>
+        <v>127412334</v>
       </c>
       <c r="B33" t="n">
-        <v>92622</v>
+        <v>5493</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4265,10 +4265,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>693054</v>
+        <v>692673</v>
       </c>
       <c r="R33" t="n">
-        <v>7149264</v>
+        <v>7149439</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4332,7 +4332,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127412365</v>
+        <v>127412363</v>
       </c>
       <c r="B34" t="n">
         <v>92622</v>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>693089</v>
+        <v>693054</v>
       </c>
       <c r="R34" t="n">
-        <v>7149223</v>
+        <v>7149264</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4438,32 +4438,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127412334</v>
+        <v>127412365</v>
       </c>
       <c r="B35" t="n">
-        <v>5493</v>
+        <v>92622</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>692673</v>
+        <v>693089</v>
       </c>
       <c r="R35" t="n">
-        <v>7149439</v>
+        <v>7149223</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4544,32 +4544,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127412360</v>
+        <v>127412324</v>
       </c>
       <c r="B36" t="n">
-        <v>92638</v>
+        <v>92610</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2059</v>
+        <v>149</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>692978</v>
+        <v>692937</v>
       </c>
       <c r="R36" t="n">
-        <v>7149291</v>
+        <v>7149228</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127412324</v>
+        <v>127412360</v>
       </c>
       <c r="B37" t="n">
-        <v>92610</v>
+        <v>92638</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>149</v>
+        <v>2059</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>692937</v>
+        <v>692978</v>
       </c>
       <c r="R37" t="n">
-        <v>7149228</v>
+        <v>7149291</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5710,7 +5710,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127412342</v>
+        <v>127412339</v>
       </c>
       <c r="B47" t="n">
         <v>92622</v>
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>692822</v>
+        <v>692742</v>
       </c>
       <c r="R47" t="n">
-        <v>7149491</v>
+        <v>7149553</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5816,7 +5816,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127412339</v>
+        <v>127412342</v>
       </c>
       <c r="B48" t="n">
         <v>92622</v>
@@ -5855,10 +5855,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>692742</v>
+        <v>692822</v>
       </c>
       <c r="R48" t="n">
-        <v>7149553</v>
+        <v>7149491</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -7088,32 +7088,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412331</v>
+        <v>127412333</v>
       </c>
       <c r="B60" t="n">
-        <v>92622</v>
+        <v>92614</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7127,10 +7127,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>692989</v>
+        <v>692649</v>
       </c>
       <c r="R60" t="n">
-        <v>7149194</v>
+        <v>7149598</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7194,7 +7194,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412370</v>
+        <v>127412362</v>
       </c>
       <c r="B61" t="n">
         <v>92622</v>
@@ -7233,10 +7233,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>693118</v>
+        <v>693013</v>
       </c>
       <c r="R61" t="n">
-        <v>7149155</v>
+        <v>7149208</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7300,32 +7300,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127412364</v>
+        <v>127412331</v>
       </c>
       <c r="B62" t="n">
-        <v>92638</v>
+        <v>92622</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>693060</v>
+        <v>692989</v>
       </c>
       <c r="R62" t="n">
-        <v>7149216</v>
+        <v>7149194</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7406,32 +7406,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127412333</v>
+        <v>127412344</v>
       </c>
       <c r="B63" t="n">
-        <v>92614</v>
+        <v>92634</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>692649</v>
+        <v>692854</v>
       </c>
       <c r="R63" t="n">
-        <v>7149598</v>
+        <v>7149427</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7512,10 +7512,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127412344</v>
+        <v>127412370</v>
       </c>
       <c r="B64" t="n">
-        <v>92634</v>
+        <v>92622</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7523,21 +7523,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>692854</v>
+        <v>693118</v>
       </c>
       <c r="R64" t="n">
-        <v>7149427</v>
+        <v>7149155</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7618,32 +7618,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412362</v>
+        <v>127412364</v>
       </c>
       <c r="B65" t="n">
-        <v>92622</v>
+        <v>92638</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7657,10 +7657,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>693013</v>
+        <v>693060</v>
       </c>
       <c r="R65" t="n">
-        <v>7149208</v>
+        <v>7149216</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7936,32 +7936,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127412350</v>
+        <v>127412353</v>
       </c>
       <c r="B68" t="n">
-        <v>92634</v>
+        <v>78779</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7975,10 +7975,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>692958</v>
+        <v>692989</v>
       </c>
       <c r="R68" t="n">
-        <v>7149383</v>
+        <v>7149374</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8042,32 +8042,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127412355</v>
+        <v>127412357</v>
       </c>
       <c r="B69" t="n">
-        <v>92622</v>
+        <v>92650</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -8081,10 +8081,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>692985</v>
+        <v>692963</v>
       </c>
       <c r="R69" t="n">
-        <v>7149369</v>
+        <v>7149329</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8148,32 +8148,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127412357</v>
+        <v>127412355</v>
       </c>
       <c r="B70" t="n">
-        <v>92650</v>
+        <v>92622</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>692963</v>
+        <v>692985</v>
       </c>
       <c r="R70" t="n">
-        <v>7149329</v>
+        <v>7149369</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8254,32 +8254,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127412353</v>
+        <v>127412350</v>
       </c>
       <c r="B71" t="n">
-        <v>78779</v>
+        <v>92634</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8293,10 +8293,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>692989</v>
+        <v>692958</v>
       </c>
       <c r="R71" t="n">
-        <v>7149374</v>
+        <v>7149383</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>

--- a/artfynd/A 52547-2020 artfynd.xlsx
+++ b/artfynd/A 52547-2020 artfynd.xlsx
@@ -3590,32 +3590,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127412327</v>
+        <v>127412326</v>
       </c>
       <c r="B27" t="n">
-        <v>92634</v>
+        <v>92638</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>692929</v>
+        <v>692934</v>
       </c>
       <c r="R27" t="n">
-        <v>7149201</v>
+        <v>7149219</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127412329</v>
+        <v>127412327</v>
       </c>
       <c r="B28" t="n">
-        <v>92622</v>
+        <v>92634</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>692950</v>
+        <v>692929</v>
       </c>
       <c r="R28" t="n">
-        <v>7149192</v>
+        <v>7149201</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3802,7 +3802,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127412322</v>
+        <v>127412329</v>
       </c>
       <c r="B29" t="n">
         <v>92622</v>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>692932</v>
+        <v>692950</v>
       </c>
       <c r="R29" t="n">
-        <v>7149288</v>
+        <v>7149192</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3908,10 +3908,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127412332</v>
+        <v>127412322</v>
       </c>
       <c r="B30" t="n">
-        <v>92634</v>
+        <v>92622</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3919,21 +3919,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>692625</v>
+        <v>692932</v>
       </c>
       <c r="R30" t="n">
-        <v>7149521</v>
+        <v>7149288</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4014,32 +4014,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127412328</v>
+        <v>127412332</v>
       </c>
       <c r="B31" t="n">
-        <v>92658</v>
+        <v>92634</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>692931</v>
+        <v>692625</v>
       </c>
       <c r="R31" t="n">
-        <v>7149192</v>
+        <v>7149521</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4120,10 +4120,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127412326</v>
+        <v>127412328</v>
       </c>
       <c r="B32" t="n">
-        <v>92638</v>
+        <v>92658</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4131,21 +4131,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>692934</v>
+        <v>692931</v>
       </c>
       <c r="R32" t="n">
-        <v>7149219</v>
+        <v>7149192</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4226,32 +4226,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127412334</v>
+        <v>127412363</v>
       </c>
       <c r="B33" t="n">
-        <v>5493</v>
+        <v>92622</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4265,10 +4265,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>692673</v>
+        <v>693054</v>
       </c>
       <c r="R33" t="n">
-        <v>7149439</v>
+        <v>7149264</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4332,7 +4332,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127412363</v>
+        <v>127412365</v>
       </c>
       <c r="B34" t="n">
         <v>92622</v>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>693054</v>
+        <v>693089</v>
       </c>
       <c r="R34" t="n">
-        <v>7149264</v>
+        <v>7149223</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4438,32 +4438,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127412365</v>
+        <v>127412334</v>
       </c>
       <c r="B35" t="n">
-        <v>92622</v>
+        <v>5493</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>693089</v>
+        <v>692673</v>
       </c>
       <c r="R35" t="n">
-        <v>7149223</v>
+        <v>7149439</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -7088,10 +7088,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412333</v>
+        <v>127412364</v>
       </c>
       <c r="B60" t="n">
-        <v>92614</v>
+        <v>92638</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7127,10 +7127,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>692649</v>
+        <v>693060</v>
       </c>
       <c r="R60" t="n">
-        <v>7149598</v>
+        <v>7149216</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7194,32 +7194,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412362</v>
+        <v>127412345</v>
       </c>
       <c r="B61" t="n">
-        <v>92622</v>
+        <v>92650</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7233,10 +7233,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>693013</v>
+        <v>692899</v>
       </c>
       <c r="R61" t="n">
-        <v>7149208</v>
+        <v>7149426</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7300,32 +7300,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127412331</v>
+        <v>127412333</v>
       </c>
       <c r="B62" t="n">
-        <v>92622</v>
+        <v>92614</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>692989</v>
+        <v>692649</v>
       </c>
       <c r="R62" t="n">
-        <v>7149194</v>
+        <v>7149598</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7406,10 +7406,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127412344</v>
+        <v>127412362</v>
       </c>
       <c r="B63" t="n">
-        <v>92634</v>
+        <v>92622</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7417,21 +7417,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>692854</v>
+        <v>693013</v>
       </c>
       <c r="R63" t="n">
-        <v>7149427</v>
+        <v>7149208</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7512,7 +7512,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127412370</v>
+        <v>127412331</v>
       </c>
       <c r="B64" t="n">
         <v>92622</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>693118</v>
+        <v>692989</v>
       </c>
       <c r="R64" t="n">
-        <v>7149155</v>
+        <v>7149194</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7618,32 +7618,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412364</v>
+        <v>127412344</v>
       </c>
       <c r="B65" t="n">
-        <v>92638</v>
+        <v>92634</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7657,10 +7657,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>693060</v>
+        <v>692854</v>
       </c>
       <c r="R65" t="n">
-        <v>7149216</v>
+        <v>7149427</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7724,32 +7724,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127412345</v>
+        <v>127412370</v>
       </c>
       <c r="B66" t="n">
-        <v>92650</v>
+        <v>92622</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>692899</v>
+        <v>693118</v>
       </c>
       <c r="R66" t="n">
-        <v>7149426</v>
+        <v>7149155</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7936,10 +7936,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127412353</v>
+        <v>127412357</v>
       </c>
       <c r="B68" t="n">
-        <v>78779</v>
+        <v>92650</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7947,21 +7947,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>5449</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7975,10 +7975,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>692989</v>
+        <v>692963</v>
       </c>
       <c r="R68" t="n">
-        <v>7149374</v>
+        <v>7149329</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8042,32 +8042,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127412357</v>
+        <v>127412355</v>
       </c>
       <c r="B69" t="n">
-        <v>92650</v>
+        <v>92622</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -8081,10 +8081,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>692963</v>
+        <v>692985</v>
       </c>
       <c r="R69" t="n">
-        <v>7149329</v>
+        <v>7149369</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8148,10 +8148,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127412355</v>
+        <v>127412350</v>
       </c>
       <c r="B70" t="n">
-        <v>92622</v>
+        <v>92634</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8159,21 +8159,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>692985</v>
+        <v>692958</v>
       </c>
       <c r="R70" t="n">
-        <v>7149369</v>
+        <v>7149383</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8254,32 +8254,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127412350</v>
+        <v>127412353</v>
       </c>
       <c r="B71" t="n">
-        <v>92634</v>
+        <v>78779</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8293,10 +8293,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>692958</v>
+        <v>692989</v>
       </c>
       <c r="R71" t="n">
-        <v>7149383</v>
+        <v>7149374</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>

--- a/artfynd/A 52547-2020 artfynd.xlsx
+++ b/artfynd/A 52547-2020 artfynd.xlsx
@@ -3696,32 +3696,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127412327</v>
+        <v>127412328</v>
       </c>
       <c r="B28" t="n">
-        <v>92634</v>
+        <v>92658</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>692929</v>
+        <v>692931</v>
       </c>
       <c r="R28" t="n">
-        <v>7149201</v>
+        <v>7149192</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3802,10 +3802,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127412329</v>
+        <v>127412327</v>
       </c>
       <c r="B29" t="n">
-        <v>92622</v>
+        <v>92634</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3813,21 +3813,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>692950</v>
+        <v>692929</v>
       </c>
       <c r="R29" t="n">
-        <v>7149192</v>
+        <v>7149201</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3908,7 +3908,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127412322</v>
+        <v>127412329</v>
       </c>
       <c r="B30" t="n">
         <v>92622</v>
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>692932</v>
+        <v>692950</v>
       </c>
       <c r="R30" t="n">
-        <v>7149288</v>
+        <v>7149192</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127412332</v>
+        <v>127412322</v>
       </c>
       <c r="B31" t="n">
-        <v>92634</v>
+        <v>92622</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4025,21 +4025,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>692625</v>
+        <v>692932</v>
       </c>
       <c r="R31" t="n">
-        <v>7149521</v>
+        <v>7149288</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4120,32 +4120,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127412328</v>
+        <v>127412332</v>
       </c>
       <c r="B32" t="n">
-        <v>92658</v>
+        <v>92634</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>692931</v>
+        <v>692625</v>
       </c>
       <c r="R32" t="n">
-        <v>7149192</v>
+        <v>7149521</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4544,32 +4544,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127412324</v>
+        <v>127412360</v>
       </c>
       <c r="B36" t="n">
-        <v>92610</v>
+        <v>92638</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>149</v>
+        <v>2059</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>692937</v>
+        <v>692978</v>
       </c>
       <c r="R36" t="n">
-        <v>7149228</v>
+        <v>7149291</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127412360</v>
+        <v>127412324</v>
       </c>
       <c r="B37" t="n">
-        <v>92638</v>
+        <v>92610</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2059</v>
+        <v>149</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>692978</v>
+        <v>692937</v>
       </c>
       <c r="R37" t="n">
-        <v>7149291</v>
+        <v>7149228</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4756,32 +4756,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127412367</v>
+        <v>127412321</v>
       </c>
       <c r="B38" t="n">
-        <v>92622</v>
+        <v>92616</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>693081</v>
+        <v>692916</v>
       </c>
       <c r="R38" t="n">
-        <v>7149184</v>
+        <v>7149304</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4862,10 +4862,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127412321</v>
+        <v>127412330</v>
       </c>
       <c r="B39" t="n">
-        <v>92616</v>
+        <v>92658</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4873,21 +4873,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>692916</v>
+        <v>692974</v>
       </c>
       <c r="R39" t="n">
-        <v>7149304</v>
+        <v>7149201</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4968,32 +4968,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127412330</v>
+        <v>127412367</v>
       </c>
       <c r="B40" t="n">
-        <v>92658</v>
+        <v>92622</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>692974</v>
+        <v>693081</v>
       </c>
       <c r="R40" t="n">
-        <v>7149201</v>
+        <v>7149184</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5710,7 +5710,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127412339</v>
+        <v>127412342</v>
       </c>
       <c r="B47" t="n">
         <v>92622</v>
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>692742</v>
+        <v>692822</v>
       </c>
       <c r="R47" t="n">
-        <v>7149553</v>
+        <v>7149491</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5816,7 +5816,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127412342</v>
+        <v>127412339</v>
       </c>
       <c r="B48" t="n">
         <v>92622</v>
@@ -5855,10 +5855,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>692822</v>
+        <v>692742</v>
       </c>
       <c r="R48" t="n">
-        <v>7149491</v>
+        <v>7149553</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6028,10 +6028,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127412352</v>
+        <v>127412320</v>
       </c>
       <c r="B50" t="n">
-        <v>79638</v>
+        <v>92648</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>5448</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>692989</v>
+        <v>692916</v>
       </c>
       <c r="R50" t="n">
-        <v>7149374</v>
+        <v>7149304</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6134,10 +6134,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127412320</v>
+        <v>127412352</v>
       </c>
       <c r="B51" t="n">
-        <v>92648</v>
+        <v>79638</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5448</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>692916</v>
+        <v>692989</v>
       </c>
       <c r="R51" t="n">
-        <v>7149304</v>
+        <v>7149374</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6770,7 +6770,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127412325</v>
+        <v>127412361</v>
       </c>
       <c r="B57" t="n">
         <v>92638</v>
@@ -6809,10 +6809,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>692939</v>
+        <v>693017</v>
       </c>
       <c r="R57" t="n">
-        <v>7149230</v>
+        <v>7149215</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6876,7 +6876,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127412361</v>
+        <v>127412325</v>
       </c>
       <c r="B58" t="n">
         <v>92638</v>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>693017</v>
+        <v>692939</v>
       </c>
       <c r="R58" t="n">
-        <v>7149215</v>
+        <v>7149230</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7194,10 +7194,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412345</v>
+        <v>127412333</v>
       </c>
       <c r="B61" t="n">
-        <v>92650</v>
+        <v>92614</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7205,21 +7205,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7233,10 +7233,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>692899</v>
+        <v>692649</v>
       </c>
       <c r="R61" t="n">
-        <v>7149426</v>
+        <v>7149598</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7300,32 +7300,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127412333</v>
+        <v>127412362</v>
       </c>
       <c r="B62" t="n">
-        <v>92614</v>
+        <v>92622</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>692649</v>
+        <v>693013</v>
       </c>
       <c r="R62" t="n">
-        <v>7149598</v>
+        <v>7149208</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7406,7 +7406,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127412362</v>
+        <v>127412331</v>
       </c>
       <c r="B63" t="n">
         <v>92622</v>
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>693013</v>
+        <v>692989</v>
       </c>
       <c r="R63" t="n">
-        <v>7149208</v>
+        <v>7149194</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7512,32 +7512,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127412331</v>
+        <v>127412345</v>
       </c>
       <c r="B64" t="n">
-        <v>92622</v>
+        <v>92650</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>692989</v>
+        <v>692899</v>
       </c>
       <c r="R64" t="n">
-        <v>7149194</v>
+        <v>7149426</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>

--- a/artfynd/A 52547-2020 artfynd.xlsx
+++ b/artfynd/A 52547-2020 artfynd.xlsx
@@ -3593,7 +3593,7 @@
         <v>127412326</v>
       </c>
       <c r="B27" t="n">
-        <v>92638</v>
+        <v>92644</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3696,32 +3696,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127412328</v>
+        <v>127412327</v>
       </c>
       <c r="B28" t="n">
-        <v>92658</v>
+        <v>92640</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>692931</v>
+        <v>692929</v>
       </c>
       <c r="R28" t="n">
-        <v>7149192</v>
+        <v>7149201</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3802,10 +3802,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127412327</v>
+        <v>127412329</v>
       </c>
       <c r="B29" t="n">
-        <v>92634</v>
+        <v>92628</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3813,21 +3813,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>692929</v>
+        <v>692950</v>
       </c>
       <c r="R29" t="n">
-        <v>7149201</v>
+        <v>7149192</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3908,10 +3908,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127412329</v>
+        <v>127412322</v>
       </c>
       <c r="B30" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>692950</v>
+        <v>692932</v>
       </c>
       <c r="R30" t="n">
-        <v>7149192</v>
+        <v>7149288</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127412322</v>
+        <v>127412332</v>
       </c>
       <c r="B31" t="n">
-        <v>92622</v>
+        <v>92640</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4025,21 +4025,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>692932</v>
+        <v>692625</v>
       </c>
       <c r="R31" t="n">
-        <v>7149288</v>
+        <v>7149521</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4120,32 +4120,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127412332</v>
+        <v>127412328</v>
       </c>
       <c r="B32" t="n">
-        <v>92634</v>
+        <v>92664</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>692625</v>
+        <v>692931</v>
       </c>
       <c r="R32" t="n">
-        <v>7149521</v>
+        <v>7149192</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4229,7 +4229,7 @@
         <v>127412363</v>
       </c>
       <c r="B33" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>127412365</v>
       </c>
       <c r="B34" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         <v>127412360</v>
       </c>
       <c r="B36" t="n">
-        <v>92638</v>
+        <v>92644</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>127412324</v>
       </c>
       <c r="B37" t="n">
-        <v>92610</v>
+        <v>92616</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4756,10 +4756,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127412321</v>
+        <v>127412330</v>
       </c>
       <c r="B38" t="n">
-        <v>92616</v>
+        <v>92664</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4767,21 +4767,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>692916</v>
+        <v>692974</v>
       </c>
       <c r="R38" t="n">
-        <v>7149304</v>
+        <v>7149201</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4862,32 +4862,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127412330</v>
+        <v>127412367</v>
       </c>
       <c r="B39" t="n">
-        <v>92658</v>
+        <v>92628</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>692974</v>
+        <v>693081</v>
       </c>
       <c r="R39" t="n">
-        <v>7149201</v>
+        <v>7149184</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4968,32 +4968,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127412367</v>
+        <v>127412321</v>
       </c>
       <c r="B40" t="n">
         <v>92622</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>693081</v>
+        <v>692916</v>
       </c>
       <c r="R40" t="n">
-        <v>7149184</v>
+        <v>7149304</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5183,7 +5183,7 @@
         <v>127412343</v>
       </c>
       <c r="B42" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>127412346</v>
       </c>
       <c r="B43" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>127412368</v>
       </c>
       <c r="B44" t="n">
-        <v>92634</v>
+        <v>92640</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>127412358</v>
       </c>
       <c r="B45" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5710,10 +5710,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127412342</v>
+        <v>127412339</v>
       </c>
       <c r="B47" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>692822</v>
+        <v>692742</v>
       </c>
       <c r="R47" t="n">
-        <v>7149491</v>
+        <v>7149553</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5816,10 +5816,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127412339</v>
+        <v>127412342</v>
       </c>
       <c r="B48" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5855,10 +5855,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>692742</v>
+        <v>692822</v>
       </c>
       <c r="R48" t="n">
-        <v>7149553</v>
+        <v>7149491</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5925,7 +5925,7 @@
         <v>127412349</v>
       </c>
       <c r="B49" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>127412320</v>
       </c>
       <c r="B50" t="n">
-        <v>92648</v>
+        <v>92654</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>127412341</v>
       </c>
       <c r="B52" t="n">
-        <v>92616</v>
+        <v>92622</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>127412359</v>
       </c>
       <c r="B53" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6452,32 +6452,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127412366</v>
+        <v>127412338</v>
       </c>
       <c r="B54" t="n">
-        <v>92638</v>
+        <v>92628</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>693119</v>
+        <v>692701</v>
       </c>
       <c r="R54" t="n">
-        <v>7149224</v>
+        <v>7149567</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6558,32 +6558,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412338</v>
+        <v>127412366</v>
       </c>
       <c r="B55" t="n">
-        <v>92622</v>
+        <v>92644</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6597,10 +6597,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>692701</v>
+        <v>693119</v>
       </c>
       <c r="R55" t="n">
-        <v>7149567</v>
+        <v>7149224</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6667,7 +6667,7 @@
         <v>127412323</v>
       </c>
       <c r="B56" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>127412361</v>
       </c>
       <c r="B57" t="n">
-        <v>92638</v>
+        <v>92644</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>127412325</v>
       </c>
       <c r="B58" t="n">
-        <v>92638</v>
+        <v>92644</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>127412364</v>
       </c>
       <c r="B60" t="n">
-        <v>92638</v>
+        <v>92644</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         <v>127412333</v>
       </c>
       <c r="B61" t="n">
-        <v>92614</v>
+        <v>92620</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>127412362</v>
       </c>
       <c r="B62" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>127412331</v>
       </c>
       <c r="B63" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>127412345</v>
       </c>
       <c r="B64" t="n">
-        <v>92650</v>
+        <v>92656</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>127412344</v>
       </c>
       <c r="B65" t="n">
-        <v>92634</v>
+        <v>92640</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>127412370</v>
       </c>
       <c r="B66" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>127412357</v>
       </c>
       <c r="B68" t="n">
-        <v>92650</v>
+        <v>92656</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
         <v>127412355</v>
       </c>
       <c r="B69" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>127412350</v>
       </c>
       <c r="B70" t="n">
-        <v>92634</v>
+        <v>92640</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>127412340</v>
       </c>
       <c r="B72" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 52547-2020 artfynd.xlsx
+++ b/artfynd/A 52547-2020 artfynd.xlsx
@@ -3593,7 +3593,7 @@
         <v>127412326</v>
       </c>
       <c r="B27" t="n">
-        <v>92644</v>
+        <v>92647</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>127412327</v>
       </c>
       <c r="B28" t="n">
-        <v>92640</v>
+        <v>92643</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>127412329</v>
       </c>
       <c r="B29" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>127412322</v>
       </c>
       <c r="B30" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>127412332</v>
       </c>
       <c r="B31" t="n">
-        <v>92640</v>
+        <v>92643</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>127412328</v>
       </c>
       <c r="B32" t="n">
-        <v>92664</v>
+        <v>92667</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>127412363</v>
       </c>
       <c r="B33" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>127412365</v>
       </c>
       <c r="B34" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4544,32 +4544,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127412360</v>
+        <v>127412324</v>
       </c>
       <c r="B36" t="n">
-        <v>92644</v>
+        <v>92619</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2059</v>
+        <v>149</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>692978</v>
+        <v>692937</v>
       </c>
       <c r="R36" t="n">
-        <v>7149291</v>
+        <v>7149228</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127412324</v>
+        <v>127412360</v>
       </c>
       <c r="B37" t="n">
-        <v>92616</v>
+        <v>92647</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>149</v>
+        <v>2059</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>692937</v>
+        <v>692978</v>
       </c>
       <c r="R37" t="n">
-        <v>7149228</v>
+        <v>7149291</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4756,10 +4756,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127412330</v>
+        <v>127412351</v>
       </c>
       <c r="B38" t="n">
-        <v>92664</v>
+        <v>79612</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4767,21 +4767,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>692974</v>
+        <v>692985</v>
       </c>
       <c r="R38" t="n">
-        <v>7149201</v>
+        <v>7149378</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4862,32 +4862,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127412367</v>
+        <v>127412330</v>
       </c>
       <c r="B39" t="n">
-        <v>92628</v>
+        <v>92667</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>693081</v>
+        <v>692974</v>
       </c>
       <c r="R39" t="n">
-        <v>7149184</v>
+        <v>7149201</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4968,32 +4968,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127412321</v>
+        <v>127412367</v>
       </c>
       <c r="B40" t="n">
-        <v>92622</v>
+        <v>92631</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>692916</v>
+        <v>693081</v>
       </c>
       <c r="R40" t="n">
-        <v>7149304</v>
+        <v>7149184</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5074,10 +5074,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127412351</v>
+        <v>127412321</v>
       </c>
       <c r="B41" t="n">
-        <v>79609</v>
+        <v>92625</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>692985</v>
+        <v>692916</v>
       </c>
       <c r="R41" t="n">
-        <v>7149378</v>
+        <v>7149304</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5183,7 +5183,7 @@
         <v>127412343</v>
       </c>
       <c r="B42" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>127412346</v>
       </c>
       <c r="B43" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>127412368</v>
       </c>
       <c r="B44" t="n">
-        <v>92640</v>
+        <v>92643</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>127412358</v>
       </c>
       <c r="B45" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>127412339</v>
       </c>
       <c r="B47" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>127412342</v>
       </c>
       <c r="B48" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>127412349</v>
       </c>
       <c r="B49" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>127412320</v>
       </c>
       <c r="B50" t="n">
-        <v>92654</v>
+        <v>92657</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>127412352</v>
       </c>
       <c r="B51" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>127412341</v>
       </c>
       <c r="B52" t="n">
-        <v>92622</v>
+        <v>92625</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>127412359</v>
       </c>
       <c r="B53" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6452,32 +6452,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127412338</v>
+        <v>127412366</v>
       </c>
       <c r="B54" t="n">
-        <v>92628</v>
+        <v>92647</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>692701</v>
+        <v>693119</v>
       </c>
       <c r="R54" t="n">
-        <v>7149567</v>
+        <v>7149224</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6558,32 +6558,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412366</v>
+        <v>127412338</v>
       </c>
       <c r="B55" t="n">
-        <v>92644</v>
+        <v>92631</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6597,10 +6597,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>693119</v>
+        <v>692701</v>
       </c>
       <c r="R55" t="n">
-        <v>7149224</v>
+        <v>7149567</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6667,7 +6667,7 @@
         <v>127412323</v>
       </c>
       <c r="B56" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>127412361</v>
       </c>
       <c r="B57" t="n">
-        <v>92644</v>
+        <v>92647</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>127412325</v>
       </c>
       <c r="B58" t="n">
-        <v>92644</v>
+        <v>92647</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>127412347</v>
       </c>
       <c r="B59" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>127412364</v>
       </c>
       <c r="B60" t="n">
-        <v>92644</v>
+        <v>92647</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         <v>127412333</v>
       </c>
       <c r="B61" t="n">
-        <v>92620</v>
+        <v>92623</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>127412362</v>
       </c>
       <c r="B62" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>127412331</v>
       </c>
       <c r="B63" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>127412345</v>
       </c>
       <c r="B64" t="n">
-        <v>92656</v>
+        <v>92659</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>127412344</v>
       </c>
       <c r="B65" t="n">
-        <v>92640</v>
+        <v>92643</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>127412370</v>
       </c>
       <c r="B66" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>127412356</v>
       </c>
       <c r="B67" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>127412357</v>
       </c>
       <c r="B68" t="n">
-        <v>92656</v>
+        <v>92659</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
         <v>127412355</v>
       </c>
       <c r="B69" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>127412350</v>
       </c>
       <c r="B70" t="n">
-        <v>92640</v>
+        <v>92643</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>127412353</v>
       </c>
       <c r="B71" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>127412340</v>
       </c>
       <c r="B72" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 52547-2020 artfynd.xlsx
+++ b/artfynd/A 52547-2020 artfynd.xlsx
@@ -3590,10 +3590,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127412326</v>
+        <v>127412328</v>
       </c>
       <c r="B27" t="n">
-        <v>92647</v>
+        <v>92675</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3601,21 +3601,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>692934</v>
+        <v>692931</v>
       </c>
       <c r="R27" t="n">
-        <v>7149219</v>
+        <v>7149192</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3696,32 +3696,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127412327</v>
+        <v>127412326</v>
       </c>
       <c r="B28" t="n">
-        <v>92643</v>
+        <v>92655</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>692929</v>
+        <v>692934</v>
       </c>
       <c r="R28" t="n">
-        <v>7149201</v>
+        <v>7149219</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3802,10 +3802,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127412329</v>
+        <v>127412327</v>
       </c>
       <c r="B29" t="n">
-        <v>92631</v>
+        <v>92651</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3813,21 +3813,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>692950</v>
+        <v>692929</v>
       </c>
       <c r="R29" t="n">
-        <v>7149192</v>
+        <v>7149201</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3908,10 +3908,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127412322</v>
+        <v>127412329</v>
       </c>
       <c r="B30" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>692932</v>
+        <v>692950</v>
       </c>
       <c r="R30" t="n">
-        <v>7149288</v>
+        <v>7149192</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127412332</v>
+        <v>127412322</v>
       </c>
       <c r="B31" t="n">
-        <v>92643</v>
+        <v>92639</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4025,21 +4025,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>692625</v>
+        <v>692932</v>
       </c>
       <c r="R31" t="n">
-        <v>7149521</v>
+        <v>7149288</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4120,32 +4120,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127412328</v>
+        <v>127412332</v>
       </c>
       <c r="B32" t="n">
-        <v>92667</v>
+        <v>92651</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>692931</v>
+        <v>692625</v>
       </c>
       <c r="R32" t="n">
-        <v>7149192</v>
+        <v>7149521</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4229,7 +4229,7 @@
         <v>127412363</v>
       </c>
       <c r="B33" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>127412365</v>
       </c>
       <c r="B34" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4544,32 +4544,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127412324</v>
+        <v>127412360</v>
       </c>
       <c r="B36" t="n">
-        <v>92619</v>
+        <v>92655</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>149</v>
+        <v>2059</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>692937</v>
+        <v>692978</v>
       </c>
       <c r="R36" t="n">
-        <v>7149228</v>
+        <v>7149291</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127412360</v>
+        <v>127412324</v>
       </c>
       <c r="B37" t="n">
-        <v>92647</v>
+        <v>92627</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2059</v>
+        <v>149</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>692978</v>
+        <v>692937</v>
       </c>
       <c r="R37" t="n">
-        <v>7149291</v>
+        <v>7149228</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4759,7 +4759,7 @@
         <v>127412351</v>
       </c>
       <c r="B38" t="n">
-        <v>79612</v>
+        <v>79618</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>127412330</v>
       </c>
       <c r="B39" t="n">
-        <v>92667</v>
+        <v>92675</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>127412367</v>
       </c>
       <c r="B40" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>127412321</v>
       </c>
       <c r="B41" t="n">
-        <v>92625</v>
+        <v>92633</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>127412343</v>
       </c>
       <c r="B42" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>127412346</v>
       </c>
       <c r="B43" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>127412368</v>
       </c>
       <c r="B44" t="n">
-        <v>92643</v>
+        <v>92651</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>127412358</v>
       </c>
       <c r="B45" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>127412339</v>
       </c>
       <c r="B47" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>127412342</v>
       </c>
       <c r="B48" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>127412349</v>
       </c>
       <c r="B49" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>127412320</v>
       </c>
       <c r="B50" t="n">
-        <v>92657</v>
+        <v>92665</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>127412352</v>
       </c>
       <c r="B51" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>127412341</v>
       </c>
       <c r="B52" t="n">
-        <v>92625</v>
+        <v>92633</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>127412359</v>
       </c>
       <c r="B53" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6452,32 +6452,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127412366</v>
+        <v>127412338</v>
       </c>
       <c r="B54" t="n">
-        <v>92647</v>
+        <v>92639</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>693119</v>
+        <v>692701</v>
       </c>
       <c r="R54" t="n">
-        <v>7149224</v>
+        <v>7149567</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6558,32 +6558,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412338</v>
+        <v>127412366</v>
       </c>
       <c r="B55" t="n">
-        <v>92631</v>
+        <v>92655</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6597,10 +6597,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>692701</v>
+        <v>693119</v>
       </c>
       <c r="R55" t="n">
-        <v>7149567</v>
+        <v>7149224</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6667,7 +6667,7 @@
         <v>127412323</v>
       </c>
       <c r="B56" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>127412361</v>
       </c>
       <c r="B57" t="n">
-        <v>92647</v>
+        <v>92655</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>127412325</v>
       </c>
       <c r="B58" t="n">
-        <v>92647</v>
+        <v>92655</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>127412347</v>
       </c>
       <c r="B59" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>127412364</v>
       </c>
       <c r="B60" t="n">
-        <v>92647</v>
+        <v>92655</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7194,10 +7194,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412333</v>
+        <v>127412345</v>
       </c>
       <c r="B61" t="n">
-        <v>92623</v>
+        <v>92667</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7205,21 +7205,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7233,10 +7233,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>692649</v>
+        <v>692899</v>
       </c>
       <c r="R61" t="n">
-        <v>7149598</v>
+        <v>7149426</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7300,32 +7300,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127412362</v>
+        <v>127412333</v>
       </c>
       <c r="B62" t="n">
         <v>92631</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>693013</v>
+        <v>692649</v>
       </c>
       <c r="R62" t="n">
-        <v>7149208</v>
+        <v>7149598</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7406,10 +7406,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127412331</v>
+        <v>127412362</v>
       </c>
       <c r="B63" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>692989</v>
+        <v>693013</v>
       </c>
       <c r="R63" t="n">
-        <v>7149194</v>
+        <v>7149208</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7512,32 +7512,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127412345</v>
+        <v>127412331</v>
       </c>
       <c r="B64" t="n">
-        <v>92659</v>
+        <v>92639</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>692899</v>
+        <v>692989</v>
       </c>
       <c r="R64" t="n">
-        <v>7149426</v>
+        <v>7149194</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7621,7 +7621,7 @@
         <v>127412344</v>
       </c>
       <c r="B65" t="n">
-        <v>92643</v>
+        <v>92651</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>127412370</v>
       </c>
       <c r="B66" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>127412356</v>
       </c>
       <c r="B67" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7936,10 +7936,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127412357</v>
+        <v>127412353</v>
       </c>
       <c r="B68" t="n">
-        <v>92659</v>
+        <v>78788</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7947,21 +7947,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7975,10 +7975,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>692963</v>
+        <v>692989</v>
       </c>
       <c r="R68" t="n">
-        <v>7149329</v>
+        <v>7149374</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8042,32 +8042,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127412355</v>
+        <v>127412357</v>
       </c>
       <c r="B69" t="n">
-        <v>92631</v>
+        <v>92667</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -8081,10 +8081,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>692985</v>
+        <v>692963</v>
       </c>
       <c r="R69" t="n">
-        <v>7149369</v>
+        <v>7149329</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8148,10 +8148,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127412350</v>
+        <v>127412355</v>
       </c>
       <c r="B70" t="n">
-        <v>92643</v>
+        <v>92639</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8159,21 +8159,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>692958</v>
+        <v>692985</v>
       </c>
       <c r="R70" t="n">
-        <v>7149383</v>
+        <v>7149369</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8254,32 +8254,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127412353</v>
+        <v>127412350</v>
       </c>
       <c r="B71" t="n">
-        <v>78782</v>
+        <v>92651</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8293,10 +8293,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>692989</v>
+        <v>692958</v>
       </c>
       <c r="R71" t="n">
-        <v>7149374</v>
+        <v>7149383</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8363,7 +8363,7 @@
         <v>127412340</v>
       </c>
       <c r="B72" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 52547-2020 artfynd.xlsx
+++ b/artfynd/A 52547-2020 artfynd.xlsx
@@ -3590,32 +3590,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127412328</v>
+        <v>127412327</v>
       </c>
       <c r="B27" t="n">
-        <v>92675</v>
+        <v>92652</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>692931</v>
+        <v>692929</v>
       </c>
       <c r="R27" t="n">
-        <v>7149192</v>
+        <v>7149201</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3699,7 +3699,7 @@
         <v>127412326</v>
       </c>
       <c r="B28" t="n">
-        <v>92655</v>
+        <v>92656</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127412327</v>
+        <v>127412329</v>
       </c>
       <c r="B29" t="n">
-        <v>92651</v>
+        <v>92640</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3813,21 +3813,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>692929</v>
+        <v>692950</v>
       </c>
       <c r="R29" t="n">
-        <v>7149201</v>
+        <v>7149192</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3908,10 +3908,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127412329</v>
+        <v>127412322</v>
       </c>
       <c r="B30" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>692950</v>
+        <v>692932</v>
       </c>
       <c r="R30" t="n">
-        <v>7149192</v>
+        <v>7149288</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127412322</v>
+        <v>127412332</v>
       </c>
       <c r="B31" t="n">
-        <v>92639</v>
+        <v>92652</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4025,21 +4025,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>692932</v>
+        <v>692625</v>
       </c>
       <c r="R31" t="n">
-        <v>7149288</v>
+        <v>7149521</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4120,32 +4120,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127412332</v>
+        <v>127412328</v>
       </c>
       <c r="B32" t="n">
-        <v>92651</v>
+        <v>92676</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>692625</v>
+        <v>692931</v>
       </c>
       <c r="R32" t="n">
-        <v>7149521</v>
+        <v>7149192</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4229,7 +4229,7 @@
         <v>127412363</v>
       </c>
       <c r="B33" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>127412365</v>
       </c>
       <c r="B34" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4544,32 +4544,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127412360</v>
+        <v>127412324</v>
       </c>
       <c r="B36" t="n">
-        <v>92655</v>
+        <v>92628</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2059</v>
+        <v>149</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>692978</v>
+        <v>692937</v>
       </c>
       <c r="R36" t="n">
-        <v>7149291</v>
+        <v>7149228</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127412324</v>
+        <v>127412360</v>
       </c>
       <c r="B37" t="n">
-        <v>92627</v>
+        <v>92656</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>149</v>
+        <v>2059</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>692937</v>
+        <v>692978</v>
       </c>
       <c r="R37" t="n">
-        <v>7149228</v>
+        <v>7149291</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4756,32 +4756,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127412351</v>
+        <v>127412367</v>
       </c>
       <c r="B38" t="n">
-        <v>79618</v>
+        <v>92640</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>692985</v>
+        <v>693081</v>
       </c>
       <c r="R38" t="n">
-        <v>7149378</v>
+        <v>7149184</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4862,10 +4862,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127412330</v>
+        <v>127412321</v>
       </c>
       <c r="B39" t="n">
-        <v>92675</v>
+        <v>92634</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4873,21 +4873,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>692974</v>
+        <v>692916</v>
       </c>
       <c r="R39" t="n">
-        <v>7149201</v>
+        <v>7149304</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4968,32 +4968,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127412367</v>
+        <v>127412330</v>
       </c>
       <c r="B40" t="n">
-        <v>92639</v>
+        <v>92676</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>693081</v>
+        <v>692974</v>
       </c>
       <c r="R40" t="n">
-        <v>7149184</v>
+        <v>7149201</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5074,10 +5074,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127412321</v>
+        <v>127412351</v>
       </c>
       <c r="B41" t="n">
-        <v>92633</v>
+        <v>79618</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4362</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>692916</v>
+        <v>692985</v>
       </c>
       <c r="R41" t="n">
-        <v>7149304</v>
+        <v>7149378</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5183,7 +5183,7 @@
         <v>127412343</v>
       </c>
       <c r="B42" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>127412346</v>
       </c>
       <c r="B43" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>127412368</v>
       </c>
       <c r="B44" t="n">
-        <v>92651</v>
+        <v>92652</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>127412358</v>
       </c>
       <c r="B45" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5710,10 +5710,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127412339</v>
+        <v>127412342</v>
       </c>
       <c r="B47" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>692742</v>
+        <v>692822</v>
       </c>
       <c r="R47" t="n">
-        <v>7149553</v>
+        <v>7149491</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5816,10 +5816,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127412342</v>
+        <v>127412339</v>
       </c>
       <c r="B48" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5855,10 +5855,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>692822</v>
+        <v>692742</v>
       </c>
       <c r="R48" t="n">
-        <v>7149491</v>
+        <v>7149553</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5925,7 +5925,7 @@
         <v>127412349</v>
       </c>
       <c r="B49" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>127412320</v>
       </c>
       <c r="B50" t="n">
-        <v>92665</v>
+        <v>92666</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>127412341</v>
       </c>
       <c r="B52" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>127412359</v>
       </c>
       <c r="B53" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6452,32 +6452,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127412338</v>
+        <v>127412366</v>
       </c>
       <c r="B54" t="n">
-        <v>92639</v>
+        <v>92656</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>692701</v>
+        <v>693119</v>
       </c>
       <c r="R54" t="n">
-        <v>7149567</v>
+        <v>7149224</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6558,32 +6558,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412366</v>
+        <v>127412338</v>
       </c>
       <c r="B55" t="n">
-        <v>92655</v>
+        <v>92640</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6597,10 +6597,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>693119</v>
+        <v>692701</v>
       </c>
       <c r="R55" t="n">
-        <v>7149224</v>
+        <v>7149567</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6667,7 +6667,7 @@
         <v>127412323</v>
       </c>
       <c r="B56" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>127412361</v>
       </c>
       <c r="B57" t="n">
-        <v>92655</v>
+        <v>92656</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>127412325</v>
       </c>
       <c r="B58" t="n">
-        <v>92655</v>
+        <v>92656</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7088,10 +7088,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412364</v>
+        <v>127412345</v>
       </c>
       <c r="B60" t="n">
-        <v>92655</v>
+        <v>92668</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7127,10 +7127,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>693060</v>
+        <v>692899</v>
       </c>
       <c r="R60" t="n">
-        <v>7149216</v>
+        <v>7149426</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7194,10 +7194,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412345</v>
+        <v>127412333</v>
       </c>
       <c r="B61" t="n">
-        <v>92667</v>
+        <v>92632</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7205,21 +7205,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7233,10 +7233,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>692899</v>
+        <v>692649</v>
       </c>
       <c r="R61" t="n">
-        <v>7149426</v>
+        <v>7149598</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7300,32 +7300,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127412333</v>
+        <v>127412362</v>
       </c>
       <c r="B62" t="n">
-        <v>92631</v>
+        <v>92640</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>692649</v>
+        <v>693013</v>
       </c>
       <c r="R62" t="n">
-        <v>7149598</v>
+        <v>7149208</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7406,10 +7406,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127412362</v>
+        <v>127412331</v>
       </c>
       <c r="B63" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>693013</v>
+        <v>692989</v>
       </c>
       <c r="R63" t="n">
-        <v>7149208</v>
+        <v>7149194</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7512,10 +7512,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127412331</v>
+        <v>127412344</v>
       </c>
       <c r="B64" t="n">
-        <v>92639</v>
+        <v>92652</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7523,21 +7523,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>692989</v>
+        <v>692854</v>
       </c>
       <c r="R64" t="n">
-        <v>7149194</v>
+        <v>7149427</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7618,10 +7618,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412344</v>
+        <v>127412370</v>
       </c>
       <c r="B65" t="n">
-        <v>92651</v>
+        <v>92640</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7629,21 +7629,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7657,10 +7657,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>692854</v>
+        <v>693118</v>
       </c>
       <c r="R65" t="n">
-        <v>7149427</v>
+        <v>7149155</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7724,32 +7724,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127412370</v>
+        <v>127412364</v>
       </c>
       <c r="B66" t="n">
-        <v>92639</v>
+        <v>92656</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>693118</v>
+        <v>693060</v>
       </c>
       <c r="R66" t="n">
-        <v>7149155</v>
+        <v>7149216</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7936,32 +7936,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127412353</v>
+        <v>127412355</v>
       </c>
       <c r="B68" t="n">
-        <v>78788</v>
+        <v>92640</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7975,10 +7975,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>692989</v>
+        <v>692985</v>
       </c>
       <c r="R68" t="n">
-        <v>7149374</v>
+        <v>7149369</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8042,32 +8042,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127412357</v>
+        <v>127412350</v>
       </c>
       <c r="B69" t="n">
-        <v>92667</v>
+        <v>92652</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -8081,10 +8081,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>692963</v>
+        <v>692958</v>
       </c>
       <c r="R69" t="n">
-        <v>7149329</v>
+        <v>7149383</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8148,32 +8148,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127412355</v>
+        <v>127412357</v>
       </c>
       <c r="B70" t="n">
-        <v>92639</v>
+        <v>92668</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>692985</v>
+        <v>692963</v>
       </c>
       <c r="R70" t="n">
-        <v>7149369</v>
+        <v>7149329</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8254,32 +8254,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127412350</v>
+        <v>127412353</v>
       </c>
       <c r="B71" t="n">
-        <v>92651</v>
+        <v>78788</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8293,10 +8293,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>692958</v>
+        <v>692989</v>
       </c>
       <c r="R71" t="n">
-        <v>7149383</v>
+        <v>7149374</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8363,7 +8363,7 @@
         <v>127412340</v>
       </c>
       <c r="B72" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 52547-2020 artfynd.xlsx
+++ b/artfynd/A 52547-2020 artfynd.xlsx
@@ -3590,32 +3590,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127412327</v>
+        <v>127412326</v>
       </c>
       <c r="B27" t="n">
-        <v>92652</v>
+        <v>92656</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>692929</v>
+        <v>692934</v>
       </c>
       <c r="R27" t="n">
-        <v>7149201</v>
+        <v>7149219</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3696,32 +3696,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127412326</v>
+        <v>127412327</v>
       </c>
       <c r="B28" t="n">
-        <v>92656</v>
+        <v>92652</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>692934</v>
+        <v>692929</v>
       </c>
       <c r="R28" t="n">
-        <v>7149219</v>
+        <v>7149201</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3802,7 +3802,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127412329</v>
+        <v>127412322</v>
       </c>
       <c r="B29" t="n">
         <v>92640</v>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>692950</v>
+        <v>692932</v>
       </c>
       <c r="R29" t="n">
-        <v>7149192</v>
+        <v>7149288</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3908,10 +3908,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127412322</v>
+        <v>127412332</v>
       </c>
       <c r="B30" t="n">
-        <v>92640</v>
+        <v>92652</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3919,21 +3919,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>692932</v>
+        <v>692625</v>
       </c>
       <c r="R30" t="n">
-        <v>7149288</v>
+        <v>7149521</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127412332</v>
+        <v>127412329</v>
       </c>
       <c r="B31" t="n">
-        <v>92652</v>
+        <v>92640</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4025,21 +4025,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>692625</v>
+        <v>692950</v>
       </c>
       <c r="R31" t="n">
-        <v>7149521</v>
+        <v>7149192</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4226,32 +4226,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127412363</v>
+        <v>127412334</v>
       </c>
       <c r="B33" t="n">
-        <v>92640</v>
+        <v>5493</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4265,10 +4265,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>693054</v>
+        <v>692673</v>
       </c>
       <c r="R33" t="n">
-        <v>7149264</v>
+        <v>7149439</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4332,7 +4332,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127412365</v>
+        <v>127412363</v>
       </c>
       <c r="B34" t="n">
         <v>92640</v>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>693089</v>
+        <v>693054</v>
       </c>
       <c r="R34" t="n">
-        <v>7149223</v>
+        <v>7149264</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4438,32 +4438,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127412334</v>
+        <v>127412365</v>
       </c>
       <c r="B35" t="n">
-        <v>5493</v>
+        <v>92640</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>692673</v>
+        <v>693089</v>
       </c>
       <c r="R35" t="n">
-        <v>7149439</v>
+        <v>7149223</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4544,32 +4544,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127412324</v>
+        <v>127412360</v>
       </c>
       <c r="B36" t="n">
-        <v>92628</v>
+        <v>92656</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>149</v>
+        <v>2059</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>692937</v>
+        <v>692978</v>
       </c>
       <c r="R36" t="n">
-        <v>7149228</v>
+        <v>7149291</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127412360</v>
+        <v>127412324</v>
       </c>
       <c r="B37" t="n">
-        <v>92656</v>
+        <v>92628</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2059</v>
+        <v>149</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>692978</v>
+        <v>692937</v>
       </c>
       <c r="R37" t="n">
-        <v>7149291</v>
+        <v>7149228</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4756,32 +4756,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127412367</v>
+        <v>127412351</v>
       </c>
       <c r="B38" t="n">
-        <v>92640</v>
+        <v>79618</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>693081</v>
+        <v>692985</v>
       </c>
       <c r="R38" t="n">
-        <v>7149184</v>
+        <v>7149378</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4862,32 +4862,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127412321</v>
+        <v>127412367</v>
       </c>
       <c r="B39" t="n">
-        <v>92634</v>
+        <v>92640</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>692916</v>
+        <v>693081</v>
       </c>
       <c r="R39" t="n">
-        <v>7149304</v>
+        <v>7149184</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4968,10 +4968,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127412330</v>
+        <v>127412321</v>
       </c>
       <c r="B40" t="n">
-        <v>92676</v>
+        <v>92634</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4979,21 +4979,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>692974</v>
+        <v>692916</v>
       </c>
       <c r="R40" t="n">
-        <v>7149201</v>
+        <v>7149304</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5074,10 +5074,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127412351</v>
+        <v>127412330</v>
       </c>
       <c r="B41" t="n">
-        <v>79618</v>
+        <v>92676</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>692985</v>
+        <v>692974</v>
       </c>
       <c r="R41" t="n">
-        <v>7149378</v>
+        <v>7149201</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5498,32 +5498,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127412358</v>
+        <v>127412348</v>
       </c>
       <c r="B45" t="n">
-        <v>92640</v>
+        <v>5493</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>692977</v>
+        <v>692895</v>
       </c>
       <c r="R45" t="n">
-        <v>7149327</v>
+        <v>7149371</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5604,32 +5604,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127412348</v>
+        <v>127412358</v>
       </c>
       <c r="B46" t="n">
-        <v>5493</v>
+        <v>92640</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5643,10 +5643,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>692895</v>
+        <v>692977</v>
       </c>
       <c r="R46" t="n">
-        <v>7149371</v>
+        <v>7149327</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5710,7 +5710,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127412342</v>
+        <v>127412339</v>
       </c>
       <c r="B47" t="n">
         <v>92640</v>
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>692822</v>
+        <v>692742</v>
       </c>
       <c r="R47" t="n">
-        <v>7149491</v>
+        <v>7149553</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5816,7 +5816,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127412339</v>
+        <v>127412342</v>
       </c>
       <c r="B48" t="n">
         <v>92640</v>
@@ -5855,10 +5855,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>692742</v>
+        <v>692822</v>
       </c>
       <c r="R48" t="n">
-        <v>7149553</v>
+        <v>7149491</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6452,32 +6452,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127412366</v>
+        <v>127412338</v>
       </c>
       <c r="B54" t="n">
-        <v>92656</v>
+        <v>92640</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>693119</v>
+        <v>692701</v>
       </c>
       <c r="R54" t="n">
-        <v>7149224</v>
+        <v>7149567</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6558,32 +6558,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412338</v>
+        <v>127412366</v>
       </c>
       <c r="B55" t="n">
-        <v>92640</v>
+        <v>92656</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6597,10 +6597,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>692701</v>
+        <v>693119</v>
       </c>
       <c r="R55" t="n">
-        <v>7149567</v>
+        <v>7149224</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7088,10 +7088,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412345</v>
+        <v>127412333</v>
       </c>
       <c r="B60" t="n">
-        <v>92668</v>
+        <v>92632</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7127,10 +7127,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>692899</v>
+        <v>692649</v>
       </c>
       <c r="R60" t="n">
-        <v>7149426</v>
+        <v>7149598</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7194,32 +7194,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412333</v>
+        <v>127412362</v>
       </c>
       <c r="B61" t="n">
-        <v>92632</v>
+        <v>92640</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7233,10 +7233,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>692649</v>
+        <v>693013</v>
       </c>
       <c r="R61" t="n">
-        <v>7149598</v>
+        <v>7149208</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7300,7 +7300,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127412362</v>
+        <v>127412331</v>
       </c>
       <c r="B62" t="n">
         <v>92640</v>
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>693013</v>
+        <v>692989</v>
       </c>
       <c r="R62" t="n">
-        <v>7149208</v>
+        <v>7149194</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7406,7 +7406,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127412331</v>
+        <v>127412370</v>
       </c>
       <c r="B63" t="n">
         <v>92640</v>
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>692989</v>
+        <v>693118</v>
       </c>
       <c r="R63" t="n">
-        <v>7149194</v>
+        <v>7149155</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7512,32 +7512,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127412344</v>
+        <v>127412364</v>
       </c>
       <c r="B64" t="n">
-        <v>92652</v>
+        <v>92656</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>692854</v>
+        <v>693060</v>
       </c>
       <c r="R64" t="n">
-        <v>7149427</v>
+        <v>7149216</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7618,32 +7618,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412370</v>
+        <v>127412345</v>
       </c>
       <c r="B65" t="n">
-        <v>92640</v>
+        <v>92668</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7657,10 +7657,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>693118</v>
+        <v>692899</v>
       </c>
       <c r="R65" t="n">
-        <v>7149155</v>
+        <v>7149426</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7724,32 +7724,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127412364</v>
+        <v>127412344</v>
       </c>
       <c r="B66" t="n">
-        <v>92656</v>
+        <v>92652</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>693060</v>
+        <v>692854</v>
       </c>
       <c r="R66" t="n">
-        <v>7149216</v>
+        <v>7149427</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7936,32 +7936,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127412355</v>
+        <v>127412357</v>
       </c>
       <c r="B68" t="n">
-        <v>92640</v>
+        <v>92668</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7975,10 +7975,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>692985</v>
+        <v>692963</v>
       </c>
       <c r="R68" t="n">
-        <v>7149369</v>
+        <v>7149329</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8042,10 +8042,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127412350</v>
+        <v>127412355</v>
       </c>
       <c r="B69" t="n">
-        <v>92652</v>
+        <v>92640</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8053,21 +8053,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -8081,10 +8081,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>692958</v>
+        <v>692985</v>
       </c>
       <c r="R69" t="n">
-        <v>7149383</v>
+        <v>7149369</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8148,32 +8148,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127412357</v>
+        <v>127412350</v>
       </c>
       <c r="B70" t="n">
-        <v>92668</v>
+        <v>92652</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>692963</v>
+        <v>692958</v>
       </c>
       <c r="R70" t="n">
-        <v>7149329</v>
+        <v>7149383</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>

--- a/artfynd/A 52547-2020 artfynd.xlsx
+++ b/artfynd/A 52547-2020 artfynd.xlsx
@@ -3593,7 +3593,7 @@
         <v>127412326</v>
       </c>
       <c r="B27" t="n">
-        <v>92656</v>
+        <v>92657</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>127412327</v>
       </c>
       <c r="B28" t="n">
-        <v>92652</v>
+        <v>92653</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127412322</v>
+        <v>127412329</v>
       </c>
       <c r="B29" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>692932</v>
+        <v>692950</v>
       </c>
       <c r="R29" t="n">
-        <v>7149288</v>
+        <v>7149192</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3908,10 +3908,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127412332</v>
+        <v>127412322</v>
       </c>
       <c r="B30" t="n">
-        <v>92652</v>
+        <v>92641</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3919,21 +3919,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>692625</v>
+        <v>692932</v>
       </c>
       <c r="R30" t="n">
-        <v>7149521</v>
+        <v>7149288</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127412329</v>
+        <v>127412332</v>
       </c>
       <c r="B31" t="n">
-        <v>92640</v>
+        <v>92653</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4025,21 +4025,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>692950</v>
+        <v>692625</v>
       </c>
       <c r="R31" t="n">
-        <v>7149192</v>
+        <v>7149521</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4123,7 +4123,7 @@
         <v>127412328</v>
       </c>
       <c r="B32" t="n">
-        <v>92676</v>
+        <v>92677</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4226,32 +4226,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127412334</v>
+        <v>127412363</v>
       </c>
       <c r="B33" t="n">
-        <v>5493</v>
+        <v>92641</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4265,10 +4265,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>692673</v>
+        <v>693054</v>
       </c>
       <c r="R33" t="n">
-        <v>7149439</v>
+        <v>7149264</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4332,10 +4332,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127412363</v>
+        <v>127412365</v>
       </c>
       <c r="B34" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>693054</v>
+        <v>693089</v>
       </c>
       <c r="R34" t="n">
-        <v>7149264</v>
+        <v>7149223</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4438,32 +4438,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127412365</v>
+        <v>127412334</v>
       </c>
       <c r="B35" t="n">
-        <v>92640</v>
+        <v>5493</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>693089</v>
+        <v>692673</v>
       </c>
       <c r="R35" t="n">
-        <v>7149223</v>
+        <v>7149439</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4544,32 +4544,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127412360</v>
+        <v>127412324</v>
       </c>
       <c r="B36" t="n">
-        <v>92656</v>
+        <v>92629</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2059</v>
+        <v>149</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>692978</v>
+        <v>692937</v>
       </c>
       <c r="R36" t="n">
-        <v>7149291</v>
+        <v>7149228</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127412324</v>
+        <v>127412360</v>
       </c>
       <c r="B37" t="n">
-        <v>92628</v>
+        <v>92657</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>149</v>
+        <v>2059</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>692937</v>
+        <v>692978</v>
       </c>
       <c r="R37" t="n">
-        <v>7149228</v>
+        <v>7149291</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4756,32 +4756,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127412351</v>
+        <v>127412367</v>
       </c>
       <c r="B38" t="n">
-        <v>79618</v>
+        <v>92641</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>692985</v>
+        <v>693081</v>
       </c>
       <c r="R38" t="n">
-        <v>7149378</v>
+        <v>7149184</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4862,32 +4862,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127412367</v>
+        <v>127412321</v>
       </c>
       <c r="B39" t="n">
-        <v>92640</v>
+        <v>92635</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>693081</v>
+        <v>692916</v>
       </c>
       <c r="R39" t="n">
-        <v>7149184</v>
+        <v>7149304</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4968,10 +4968,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127412321</v>
+        <v>127412330</v>
       </c>
       <c r="B40" t="n">
-        <v>92634</v>
+        <v>92677</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4979,21 +4979,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>692916</v>
+        <v>692974</v>
       </c>
       <c r="R40" t="n">
-        <v>7149304</v>
+        <v>7149201</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5074,10 +5074,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127412330</v>
+        <v>127412351</v>
       </c>
       <c r="B41" t="n">
-        <v>92676</v>
+        <v>79618</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>692974</v>
+        <v>692985</v>
       </c>
       <c r="R41" t="n">
-        <v>7149201</v>
+        <v>7149378</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5183,7 +5183,7 @@
         <v>127412343</v>
       </c>
       <c r="B42" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5286,32 +5286,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127412346</v>
+        <v>127412348</v>
       </c>
       <c r="B43" t="n">
-        <v>92640</v>
+        <v>5493</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>692896</v>
+        <v>692895</v>
       </c>
       <c r="R43" t="n">
-        <v>7149409</v>
+        <v>7149371</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5392,10 +5392,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127412368</v>
+        <v>127412346</v>
       </c>
       <c r="B44" t="n">
-        <v>92652</v>
+        <v>92641</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5403,21 +5403,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>693101</v>
+        <v>692896</v>
       </c>
       <c r="R44" t="n">
-        <v>7149176</v>
+        <v>7149409</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5498,32 +5498,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127412348</v>
+        <v>127412368</v>
       </c>
       <c r="B45" t="n">
-        <v>5493</v>
+        <v>92653</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>101410</v>
+        <v>4366</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>692895</v>
+        <v>693101</v>
       </c>
       <c r="R45" t="n">
-        <v>7149371</v>
+        <v>7149176</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5607,7 +5607,7 @@
         <v>127412358</v>
       </c>
       <c r="B46" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>127412339</v>
       </c>
       <c r="B47" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>127412342</v>
       </c>
       <c r="B48" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>127412349</v>
       </c>
       <c r="B49" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6028,10 +6028,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127412320</v>
+        <v>127412352</v>
       </c>
       <c r="B50" t="n">
-        <v>92666</v>
+        <v>79647</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5448</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>692916</v>
+        <v>692989</v>
       </c>
       <c r="R50" t="n">
-        <v>7149304</v>
+        <v>7149374</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6134,10 +6134,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127412352</v>
+        <v>127412320</v>
       </c>
       <c r="B51" t="n">
-        <v>79647</v>
+        <v>92667</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>5448</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>692989</v>
+        <v>692916</v>
       </c>
       <c r="R51" t="n">
-        <v>7149374</v>
+        <v>7149304</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6243,7 +6243,7 @@
         <v>127412341</v>
       </c>
       <c r="B52" t="n">
-        <v>92634</v>
+        <v>92635</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>127412359</v>
       </c>
       <c r="B53" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>127412338</v>
       </c>
       <c r="B54" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>127412366</v>
       </c>
       <c r="B55" t="n">
-        <v>92656</v>
+        <v>92657</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>127412323</v>
       </c>
       <c r="B56" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6770,10 +6770,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127412361</v>
+        <v>127412325</v>
       </c>
       <c r="B57" t="n">
-        <v>92656</v>
+        <v>92657</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6809,10 +6809,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>693017</v>
+        <v>692939</v>
       </c>
       <c r="R57" t="n">
-        <v>7149215</v>
+        <v>7149230</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6876,10 +6876,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127412325</v>
+        <v>127412361</v>
       </c>
       <c r="B58" t="n">
-        <v>92656</v>
+        <v>92657</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>692939</v>
+        <v>693017</v>
       </c>
       <c r="R58" t="n">
-        <v>7149230</v>
+        <v>7149215</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7088,10 +7088,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412333</v>
+        <v>127412364</v>
       </c>
       <c r="B60" t="n">
-        <v>92632</v>
+        <v>92657</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7127,10 +7127,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>692649</v>
+        <v>693060</v>
       </c>
       <c r="R60" t="n">
-        <v>7149598</v>
+        <v>7149216</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7194,32 +7194,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412362</v>
+        <v>127412333</v>
       </c>
       <c r="B61" t="n">
-        <v>92640</v>
+        <v>92633</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7233,10 +7233,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>693013</v>
+        <v>692649</v>
       </c>
       <c r="R61" t="n">
-        <v>7149208</v>
+        <v>7149598</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7300,10 +7300,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127412331</v>
+        <v>127412362</v>
       </c>
       <c r="B62" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>692989</v>
+        <v>693013</v>
       </c>
       <c r="R62" t="n">
-        <v>7149194</v>
+        <v>7149208</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7406,10 +7406,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127412370</v>
+        <v>127412331</v>
       </c>
       <c r="B63" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>693118</v>
+        <v>692989</v>
       </c>
       <c r="R63" t="n">
-        <v>7149155</v>
+        <v>7149194</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7512,32 +7512,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127412364</v>
+        <v>127412344</v>
       </c>
       <c r="B64" t="n">
-        <v>92656</v>
+        <v>92653</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>693060</v>
+        <v>692854</v>
       </c>
       <c r="R64" t="n">
-        <v>7149216</v>
+        <v>7149427</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7618,32 +7618,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412345</v>
+        <v>127412370</v>
       </c>
       <c r="B65" t="n">
-        <v>92668</v>
+        <v>92641</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7657,10 +7657,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>692899</v>
+        <v>693118</v>
       </c>
       <c r="R65" t="n">
-        <v>7149426</v>
+        <v>7149155</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7724,32 +7724,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127412344</v>
+        <v>127412345</v>
       </c>
       <c r="B66" t="n">
-        <v>92652</v>
+        <v>92669</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>692854</v>
+        <v>692899</v>
       </c>
       <c r="R66" t="n">
-        <v>7149427</v>
+        <v>7149426</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7936,10 +7936,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127412357</v>
+        <v>127412353</v>
       </c>
       <c r="B68" t="n">
-        <v>92668</v>
+        <v>78788</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7947,21 +7947,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7975,10 +7975,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>692963</v>
+        <v>692989</v>
       </c>
       <c r="R68" t="n">
-        <v>7149329</v>
+        <v>7149374</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8045,7 +8045,7 @@
         <v>127412355</v>
       </c>
       <c r="B69" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>127412350</v>
       </c>
       <c r="B70" t="n">
-        <v>92652</v>
+        <v>92653</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8254,10 +8254,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127412353</v>
+        <v>127412357</v>
       </c>
       <c r="B71" t="n">
-        <v>78788</v>
+        <v>92669</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8265,21 +8265,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>5449</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8293,10 +8293,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>692989</v>
+        <v>692963</v>
       </c>
       <c r="R71" t="n">
-        <v>7149374</v>
+        <v>7149329</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8363,7 +8363,7 @@
         <v>127412340</v>
       </c>
       <c r="B72" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 52547-2020 artfynd.xlsx
+++ b/artfynd/A 52547-2020 artfynd.xlsx
@@ -3590,32 +3590,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127412326</v>
+        <v>127412332</v>
       </c>
       <c r="B27" t="n">
-        <v>92657</v>
+        <v>92654</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>692934</v>
+        <v>692625</v>
       </c>
       <c r="R27" t="n">
-        <v>7149219</v>
+        <v>7149521</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127412327</v>
+        <v>127412329</v>
       </c>
       <c r="B28" t="n">
-        <v>92653</v>
+        <v>92642</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>692929</v>
+        <v>692950</v>
       </c>
       <c r="R28" t="n">
-        <v>7149201</v>
+        <v>7149192</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3802,10 +3802,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127412329</v>
+        <v>127412322</v>
       </c>
       <c r="B29" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>692950</v>
+        <v>692932</v>
       </c>
       <c r="R29" t="n">
-        <v>7149192</v>
+        <v>7149288</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3908,32 +3908,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127412322</v>
+        <v>127412326</v>
       </c>
       <c r="B30" t="n">
-        <v>92641</v>
+        <v>92658</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>692932</v>
+        <v>692934</v>
       </c>
       <c r="R30" t="n">
-        <v>7149288</v>
+        <v>7149219</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127412332</v>
+        <v>127412327</v>
       </c>
       <c r="B31" t="n">
-        <v>92653</v>
+        <v>92654</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>692625</v>
+        <v>692929</v>
       </c>
       <c r="R31" t="n">
-        <v>7149521</v>
+        <v>7149201</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4123,7 +4123,7 @@
         <v>127412328</v>
       </c>
       <c r="B32" t="n">
-        <v>92677</v>
+        <v>92678</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4226,32 +4226,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127412363</v>
+        <v>127412334</v>
       </c>
       <c r="B33" t="n">
-        <v>92641</v>
+        <v>5493</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4265,10 +4265,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>693054</v>
+        <v>692673</v>
       </c>
       <c r="R33" t="n">
-        <v>7149264</v>
+        <v>7149439</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4332,10 +4332,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127412365</v>
+        <v>127412363</v>
       </c>
       <c r="B34" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>693089</v>
+        <v>693054</v>
       </c>
       <c r="R34" t="n">
-        <v>7149223</v>
+        <v>7149264</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4438,32 +4438,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127412334</v>
+        <v>127412365</v>
       </c>
       <c r="B35" t="n">
-        <v>5493</v>
+        <v>92642</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>692673</v>
+        <v>693089</v>
       </c>
       <c r="R35" t="n">
-        <v>7149439</v>
+        <v>7149223</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4544,32 +4544,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127412324</v>
+        <v>127412360</v>
       </c>
       <c r="B36" t="n">
-        <v>92629</v>
+        <v>92658</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>149</v>
+        <v>2059</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>692937</v>
+        <v>692978</v>
       </c>
       <c r="R36" t="n">
-        <v>7149228</v>
+        <v>7149291</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127412360</v>
+        <v>127412324</v>
       </c>
       <c r="B37" t="n">
-        <v>92657</v>
+        <v>92630</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2059</v>
+        <v>149</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>692978</v>
+        <v>692937</v>
       </c>
       <c r="R37" t="n">
-        <v>7149291</v>
+        <v>7149228</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4759,7 +4759,7 @@
         <v>127412367</v>
       </c>
       <c r="B38" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>127412321</v>
       </c>
       <c r="B39" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>127412330</v>
       </c>
       <c r="B40" t="n">
-        <v>92677</v>
+        <v>92678</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>127412343</v>
       </c>
       <c r="B42" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>127412346</v>
       </c>
       <c r="B44" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>127412368</v>
       </c>
       <c r="B45" t="n">
-        <v>92653</v>
+        <v>92654</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>127412358</v>
       </c>
       <c r="B46" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5710,10 +5710,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127412339</v>
+        <v>127412342</v>
       </c>
       <c r="B47" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>692742</v>
+        <v>692822</v>
       </c>
       <c r="R47" t="n">
-        <v>7149553</v>
+        <v>7149491</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5816,10 +5816,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127412342</v>
+        <v>127412339</v>
       </c>
       <c r="B48" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5855,10 +5855,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>692822</v>
+        <v>692742</v>
       </c>
       <c r="R48" t="n">
-        <v>7149491</v>
+        <v>7149553</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5925,7 +5925,7 @@
         <v>127412349</v>
       </c>
       <c r="B49" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>127412320</v>
       </c>
       <c r="B51" t="n">
-        <v>92667</v>
+        <v>92668</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>127412341</v>
       </c>
       <c r="B52" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>127412359</v>
       </c>
       <c r="B53" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6452,32 +6452,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127412338</v>
+        <v>127412366</v>
       </c>
       <c r="B54" t="n">
-        <v>92641</v>
+        <v>92658</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>692701</v>
+        <v>693119</v>
       </c>
       <c r="R54" t="n">
-        <v>7149567</v>
+        <v>7149224</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6558,32 +6558,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412366</v>
+        <v>127412338</v>
       </c>
       <c r="B55" t="n">
-        <v>92657</v>
+        <v>92642</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6597,10 +6597,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>693119</v>
+        <v>692701</v>
       </c>
       <c r="R55" t="n">
-        <v>7149224</v>
+        <v>7149567</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6667,7 +6667,7 @@
         <v>127412323</v>
       </c>
       <c r="B56" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>127412325</v>
       </c>
       <c r="B57" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>127412361</v>
       </c>
       <c r="B58" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7088,32 +7088,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412364</v>
+        <v>127412331</v>
       </c>
       <c r="B60" t="n">
-        <v>92657</v>
+        <v>92642</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7127,10 +7127,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>693060</v>
+        <v>692989</v>
       </c>
       <c r="R60" t="n">
-        <v>7149216</v>
+        <v>7149194</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7194,32 +7194,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412333</v>
+        <v>127412370</v>
       </c>
       <c r="B61" t="n">
-        <v>92633</v>
+        <v>92642</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7233,10 +7233,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>692649</v>
+        <v>693118</v>
       </c>
       <c r="R61" t="n">
-        <v>7149598</v>
+        <v>7149155</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7300,32 +7300,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127412362</v>
+        <v>127412364</v>
       </c>
       <c r="B62" t="n">
-        <v>92641</v>
+        <v>92658</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>693013</v>
+        <v>693060</v>
       </c>
       <c r="R62" t="n">
-        <v>7149208</v>
+        <v>7149216</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7406,32 +7406,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127412331</v>
+        <v>127412333</v>
       </c>
       <c r="B63" t="n">
-        <v>92641</v>
+        <v>92634</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>692989</v>
+        <v>692649</v>
       </c>
       <c r="R63" t="n">
-        <v>7149194</v>
+        <v>7149598</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7515,7 +7515,7 @@
         <v>127412344</v>
       </c>
       <c r="B64" t="n">
-        <v>92653</v>
+        <v>92654</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7618,10 +7618,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412370</v>
+        <v>127412362</v>
       </c>
       <c r="B65" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7657,10 +7657,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>693118</v>
+        <v>693013</v>
       </c>
       <c r="R65" t="n">
-        <v>7149155</v>
+        <v>7149208</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7727,7 +7727,7 @@
         <v>127412345</v>
       </c>
       <c r="B66" t="n">
-        <v>92669</v>
+        <v>92670</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7936,32 +7936,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127412353</v>
+        <v>127412350</v>
       </c>
       <c r="B68" t="n">
-        <v>78788</v>
+        <v>92654</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7975,10 +7975,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>692989</v>
+        <v>692958</v>
       </c>
       <c r="R68" t="n">
-        <v>7149374</v>
+        <v>7149383</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8045,7 +8045,7 @@
         <v>127412355</v>
       </c>
       <c r="B69" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8148,32 +8148,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127412350</v>
+        <v>127412357</v>
       </c>
       <c r="B70" t="n">
-        <v>92653</v>
+        <v>92670</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>692958</v>
+        <v>692963</v>
       </c>
       <c r="R70" t="n">
-        <v>7149383</v>
+        <v>7149329</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8254,10 +8254,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127412357</v>
+        <v>127412353</v>
       </c>
       <c r="B71" t="n">
-        <v>92669</v>
+        <v>78788</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8265,21 +8265,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8293,10 +8293,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>692963</v>
+        <v>692989</v>
       </c>
       <c r="R71" t="n">
-        <v>7149329</v>
+        <v>7149374</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8363,7 +8363,7 @@
         <v>127412340</v>
       </c>
       <c r="B72" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 52547-2020 artfynd.xlsx
+++ b/artfynd/A 52547-2020 artfynd.xlsx
@@ -3590,32 +3590,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127412332</v>
+        <v>127412326</v>
       </c>
       <c r="B27" t="n">
-        <v>92654</v>
+        <v>92658</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>692625</v>
+        <v>692934</v>
       </c>
       <c r="R27" t="n">
-        <v>7149521</v>
+        <v>7149219</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127412329</v>
+        <v>127412327</v>
       </c>
       <c r="B28" t="n">
-        <v>92642</v>
+        <v>92654</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>692950</v>
+        <v>692929</v>
       </c>
       <c r="R28" t="n">
-        <v>7149192</v>
+        <v>7149201</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3802,7 +3802,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127412322</v>
+        <v>127412329</v>
       </c>
       <c r="B29" t="n">
         <v>92642</v>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>692932</v>
+        <v>692950</v>
       </c>
       <c r="R29" t="n">
-        <v>7149288</v>
+        <v>7149192</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3908,32 +3908,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127412326</v>
+        <v>127412322</v>
       </c>
       <c r="B30" t="n">
-        <v>92658</v>
+        <v>92642</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>692934</v>
+        <v>692932</v>
       </c>
       <c r="R30" t="n">
-        <v>7149219</v>
+        <v>7149288</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127412327</v>
+        <v>127412332</v>
       </c>
       <c r="B31" t="n">
         <v>92654</v>
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>692929</v>
+        <v>692625</v>
       </c>
       <c r="R31" t="n">
-        <v>7149201</v>
+        <v>7149521</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4226,32 +4226,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127412334</v>
+        <v>127412363</v>
       </c>
       <c r="B33" t="n">
-        <v>5493</v>
+        <v>92642</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4265,10 +4265,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>692673</v>
+        <v>693054</v>
       </c>
       <c r="R33" t="n">
-        <v>7149439</v>
+        <v>7149264</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4332,7 +4332,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127412363</v>
+        <v>127412365</v>
       </c>
       <c r="B34" t="n">
         <v>92642</v>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>693054</v>
+        <v>693089</v>
       </c>
       <c r="R34" t="n">
-        <v>7149264</v>
+        <v>7149223</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4438,32 +4438,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127412365</v>
+        <v>127412334</v>
       </c>
       <c r="B35" t="n">
-        <v>92642</v>
+        <v>5493</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>693089</v>
+        <v>692673</v>
       </c>
       <c r="R35" t="n">
-        <v>7149223</v>
+        <v>7149439</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4544,32 +4544,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127412360</v>
+        <v>127412324</v>
       </c>
       <c r="B36" t="n">
-        <v>92658</v>
+        <v>92630</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2059</v>
+        <v>149</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>692978</v>
+        <v>692937</v>
       </c>
       <c r="R36" t="n">
-        <v>7149291</v>
+        <v>7149228</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127412324</v>
+        <v>127412360</v>
       </c>
       <c r="B37" t="n">
-        <v>92630</v>
+        <v>92658</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>149</v>
+        <v>2059</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>692937</v>
+        <v>692978</v>
       </c>
       <c r="R37" t="n">
-        <v>7149228</v>
+        <v>7149291</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5286,32 +5286,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127412348</v>
+        <v>127412346</v>
       </c>
       <c r="B43" t="n">
-        <v>5493</v>
+        <v>92642</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>692895</v>
+        <v>692896</v>
       </c>
       <c r="R43" t="n">
-        <v>7149371</v>
+        <v>7149409</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5392,10 +5392,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127412346</v>
+        <v>127412368</v>
       </c>
       <c r="B44" t="n">
-        <v>92642</v>
+        <v>92654</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5403,21 +5403,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>692896</v>
+        <v>693101</v>
       </c>
       <c r="R44" t="n">
-        <v>7149409</v>
+        <v>7149176</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5498,10 +5498,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127412368</v>
+        <v>127412358</v>
       </c>
       <c r="B45" t="n">
-        <v>92654</v>
+        <v>92642</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5509,21 +5509,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>693101</v>
+        <v>692977</v>
       </c>
       <c r="R45" t="n">
-        <v>7149176</v>
+        <v>7149327</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5604,32 +5604,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127412358</v>
+        <v>127412348</v>
       </c>
       <c r="B46" t="n">
-        <v>92642</v>
+        <v>5493</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5643,10 +5643,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>692977</v>
+        <v>692895</v>
       </c>
       <c r="R46" t="n">
-        <v>7149327</v>
+        <v>7149371</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5710,7 +5710,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127412342</v>
+        <v>127412339</v>
       </c>
       <c r="B47" t="n">
         <v>92642</v>
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>692822</v>
+        <v>692742</v>
       </c>
       <c r="R47" t="n">
-        <v>7149491</v>
+        <v>7149553</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5816,7 +5816,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127412339</v>
+        <v>127412342</v>
       </c>
       <c r="B48" t="n">
         <v>92642</v>
@@ -5855,10 +5855,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>692742</v>
+        <v>692822</v>
       </c>
       <c r="R48" t="n">
-        <v>7149553</v>
+        <v>7149491</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6028,10 +6028,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127412352</v>
+        <v>127412320</v>
       </c>
       <c r="B50" t="n">
-        <v>79647</v>
+        <v>92668</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>5448</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>692989</v>
+        <v>692916</v>
       </c>
       <c r="R50" t="n">
-        <v>7149374</v>
+        <v>7149304</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6134,10 +6134,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127412320</v>
+        <v>127412352</v>
       </c>
       <c r="B51" t="n">
-        <v>92668</v>
+        <v>79647</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5448</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>692916</v>
+        <v>692989</v>
       </c>
       <c r="R51" t="n">
-        <v>7149304</v>
+        <v>7149374</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6770,7 +6770,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127412325</v>
+        <v>127412361</v>
       </c>
       <c r="B57" t="n">
         <v>92658</v>
@@ -6809,10 +6809,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>692939</v>
+        <v>693017</v>
       </c>
       <c r="R57" t="n">
-        <v>7149230</v>
+        <v>7149215</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6876,7 +6876,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127412361</v>
+        <v>127412325</v>
       </c>
       <c r="B58" t="n">
         <v>92658</v>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>693017</v>
+        <v>692939</v>
       </c>
       <c r="R58" t="n">
-        <v>7149215</v>
+        <v>7149230</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7088,32 +7088,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412331</v>
+        <v>127412364</v>
       </c>
       <c r="B60" t="n">
-        <v>92642</v>
+        <v>92658</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7127,10 +7127,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>692989</v>
+        <v>693060</v>
       </c>
       <c r="R60" t="n">
-        <v>7149194</v>
+        <v>7149216</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7194,7 +7194,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412370</v>
+        <v>127412362</v>
       </c>
       <c r="B61" t="n">
         <v>92642</v>
@@ -7233,10 +7233,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>693118</v>
+        <v>693013</v>
       </c>
       <c r="R61" t="n">
-        <v>7149155</v>
+        <v>7149208</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7300,32 +7300,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127412364</v>
+        <v>127412331</v>
       </c>
       <c r="B62" t="n">
-        <v>92658</v>
+        <v>92642</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>693060</v>
+        <v>692989</v>
       </c>
       <c r="R62" t="n">
-        <v>7149216</v>
+        <v>7149194</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7406,32 +7406,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127412333</v>
+        <v>127412344</v>
       </c>
       <c r="B63" t="n">
-        <v>92634</v>
+        <v>92654</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>692649</v>
+        <v>692854</v>
       </c>
       <c r="R63" t="n">
-        <v>7149598</v>
+        <v>7149427</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7512,10 +7512,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127412344</v>
+        <v>127412370</v>
       </c>
       <c r="B64" t="n">
-        <v>92654</v>
+        <v>92642</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7523,21 +7523,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>692854</v>
+        <v>693118</v>
       </c>
       <c r="R64" t="n">
-        <v>7149427</v>
+        <v>7149155</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7618,32 +7618,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412362</v>
+        <v>127412333</v>
       </c>
       <c r="B65" t="n">
-        <v>92642</v>
+        <v>92634</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7657,10 +7657,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>693013</v>
+        <v>692649</v>
       </c>
       <c r="R65" t="n">
-        <v>7149208</v>
+        <v>7149598</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7936,10 +7936,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127412350</v>
+        <v>127412355</v>
       </c>
       <c r="B68" t="n">
-        <v>92654</v>
+        <v>92642</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7947,21 +7947,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7975,10 +7975,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>692958</v>
+        <v>692985</v>
       </c>
       <c r="R68" t="n">
-        <v>7149383</v>
+        <v>7149369</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8042,10 +8042,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127412355</v>
+        <v>127412350</v>
       </c>
       <c r="B69" t="n">
-        <v>92642</v>
+        <v>92654</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8053,21 +8053,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -8081,10 +8081,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>692985</v>
+        <v>692958</v>
       </c>
       <c r="R69" t="n">
-        <v>7149369</v>
+        <v>7149383</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8148,10 +8148,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127412357</v>
+        <v>127412353</v>
       </c>
       <c r="B70" t="n">
-        <v>92670</v>
+        <v>78788</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8159,21 +8159,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>692963</v>
+        <v>692989</v>
       </c>
       <c r="R70" t="n">
-        <v>7149329</v>
+        <v>7149374</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8254,10 +8254,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127412353</v>
+        <v>127412357</v>
       </c>
       <c r="B71" t="n">
-        <v>78788</v>
+        <v>92670</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8265,21 +8265,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>5449</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8293,10 +8293,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>692989</v>
+        <v>692963</v>
       </c>
       <c r="R71" t="n">
-        <v>7149374</v>
+        <v>7149329</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>

--- a/artfynd/A 52547-2020 artfynd.xlsx
+++ b/artfynd/A 52547-2020 artfynd.xlsx
@@ -4226,32 +4226,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127412363</v>
+        <v>127412334</v>
       </c>
       <c r="B33" t="n">
-        <v>92642</v>
+        <v>5493</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4265,10 +4265,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>693054</v>
+        <v>692673</v>
       </c>
       <c r="R33" t="n">
-        <v>7149264</v>
+        <v>7149439</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4332,7 +4332,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127412365</v>
+        <v>127412363</v>
       </c>
       <c r="B34" t="n">
         <v>92642</v>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>693089</v>
+        <v>693054</v>
       </c>
       <c r="R34" t="n">
-        <v>7149223</v>
+        <v>7149264</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4438,32 +4438,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127412334</v>
+        <v>127412365</v>
       </c>
       <c r="B35" t="n">
-        <v>5493</v>
+        <v>92642</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>692673</v>
+        <v>693089</v>
       </c>
       <c r="R35" t="n">
-        <v>7149439</v>
+        <v>7149223</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4756,32 +4756,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127412367</v>
+        <v>127412351</v>
       </c>
       <c r="B38" t="n">
-        <v>92642</v>
+        <v>79618</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>693081</v>
+        <v>692985</v>
       </c>
       <c r="R38" t="n">
-        <v>7149184</v>
+        <v>7149378</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4862,10 +4862,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127412321</v>
+        <v>127412330</v>
       </c>
       <c r="B39" t="n">
-        <v>92636</v>
+        <v>92678</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4873,21 +4873,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>692916</v>
+        <v>692974</v>
       </c>
       <c r="R39" t="n">
-        <v>7149304</v>
+        <v>7149201</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4968,32 +4968,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127412330</v>
+        <v>127412367</v>
       </c>
       <c r="B40" t="n">
-        <v>92678</v>
+        <v>92642</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>692974</v>
+        <v>693081</v>
       </c>
       <c r="R40" t="n">
-        <v>7149201</v>
+        <v>7149184</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5074,10 +5074,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127412351</v>
+        <v>127412321</v>
       </c>
       <c r="B41" t="n">
-        <v>79618</v>
+        <v>92636</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>692985</v>
+        <v>692916</v>
       </c>
       <c r="R41" t="n">
-        <v>7149378</v>
+        <v>7149304</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
